--- a/research/traditional_assets/database/data/malaysia/malaysia_advertising.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_advertising.xlsx
@@ -1635,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1772,22 +1772,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1179914357732772</v>
+        <v>0.1177424563274214</v>
       </c>
       <c r="C2">
-        <v>20.06078228766759</v>
+        <v>19.9158561317492</v>
       </c>
       <c r="D2">
-        <v>18.60078228766759</v>
+        <v>18.6651561317492</v>
       </c>
       <c r="E2">
-        <v>-6.63</v>
+        <v>-6.4207</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2093</v>
       </c>
       <c r="G2">
         <v>1.46</v>
@@ -1808,28 +1808,28 @@
         <v>3.11</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01052779</v>
       </c>
       <c r="N2">
-        <v>3.11</v>
+        <v>3.09947221</v>
       </c>
       <c r="O2">
-        <v>0.7464</v>
+        <v>0.7438733304</v>
       </c>
       <c r="P2">
-        <v>2.3636</v>
+        <v>2.3555988796</v>
       </c>
       <c r="Q2">
-        <v>3.7036</v>
+        <v>3.6955988796</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1179914357732772</v>
+        <v>0.118545632653961</v>
       </c>
       <c r="T2">
-        <v>1.217251318914063</v>
+        <v>1.226595874493605</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>295.4086280216455</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1854,22 +1854,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1177424563274214</v>
+        <v>0.1174934768815655</v>
       </c>
       <c r="C3">
-        <v>19.9158561317492</v>
+        <v>19.77137709500327</v>
       </c>
       <c r="D3">
-        <v>18.6651561317492</v>
+        <v>18.72997709500327</v>
       </c>
       <c r="E3">
-        <v>-6.4207</v>
+        <v>-6.2114</v>
       </c>
       <c r="F3">
-        <v>0.2093</v>
+        <v>0.4186</v>
       </c>
       <c r="G3">
         <v>1.46</v>
@@ -1890,28 +1890,28 @@
         <v>3.11</v>
       </c>
       <c r="M3">
-        <v>0.01052779</v>
+        <v>0.02105558</v>
       </c>
       <c r="N3">
-        <v>3.09947221</v>
+        <v>3.08894442</v>
       </c>
       <c r="O3">
-        <v>0.7438733304</v>
+        <v>0.7413466607999999</v>
       </c>
       <c r="P3">
-        <v>2.3555988796</v>
+        <v>2.3475977592</v>
       </c>
       <c r="Q3">
-        <v>3.6955988796</v>
+        <v>3.6875977592</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.118545632653961</v>
+        <v>0.1191111396750668</v>
       </c>
       <c r="T3">
-        <v>1.226595874493605</v>
+        <v>1.236131135289056</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>295.4086280216455</v>
+        <v>147.7043140108228</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1936,22 +1936,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1174934768815655</v>
+        <v>0.1172444974357096</v>
       </c>
       <c r="C4">
-        <v>19.77137709500327</v>
+        <v>19.62734985197386</v>
       </c>
       <c r="D4">
-        <v>18.72997709500327</v>
+        <v>18.79524985197386</v>
       </c>
       <c r="E4">
-        <v>-6.2114</v>
+        <v>-6.0021</v>
       </c>
       <c r="F4">
-        <v>0.4186</v>
+        <v>0.6279</v>
       </c>
       <c r="G4">
         <v>1.46</v>
@@ -1972,28 +1972,28 @@
         <v>3.11</v>
       </c>
       <c r="M4">
-        <v>0.02105558</v>
+        <v>0.03158337</v>
       </c>
       <c r="N4">
-        <v>3.08894442</v>
+        <v>3.07841663</v>
       </c>
       <c r="O4">
-        <v>0.7413466607999999</v>
+        <v>0.7388199912</v>
       </c>
       <c r="P4">
-        <v>2.3475977592</v>
+        <v>2.3395966388</v>
       </c>
       <c r="Q4">
-        <v>3.6875977592</v>
+        <v>3.6795966388</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1191111396750668</v>
+        <v>0.1196883066347522</v>
       </c>
       <c r="T4">
-        <v>1.236131135289056</v>
+        <v>1.245862999399878</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>147.7043140108228</v>
+        <v>98.46954267388186</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2018,22 +2018,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1172444974357096</v>
+        <v>0.1169955179898538</v>
       </c>
       <c r="C5">
-        <v>19.62734985197386</v>
+        <v>19.48377914259484</v>
       </c>
       <c r="D5">
-        <v>18.79524985197386</v>
+        <v>18.86097914259484</v>
       </c>
       <c r="E5">
-        <v>-6.0021</v>
+        <v>-5.7928</v>
       </c>
       <c r="F5">
-        <v>0.6279</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="G5">
         <v>1.46</v>
@@ -2054,28 +2054,28 @@
         <v>3.11</v>
       </c>
       <c r="M5">
-        <v>0.03158337</v>
+        <v>0.04211116</v>
       </c>
       <c r="N5">
-        <v>3.07841663</v>
+        <v>3.06788884</v>
       </c>
       <c r="O5">
-        <v>0.7388199912</v>
+        <v>0.7362933215999999</v>
       </c>
       <c r="P5">
-        <v>2.3395966388</v>
+        <v>2.3315955184</v>
       </c>
       <c r="Q5">
-        <v>3.6795966388</v>
+        <v>3.6715955184</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1196883066347522</v>
+        <v>0.1202774979060977</v>
       </c>
       <c r="T5">
-        <v>1.245862999399878</v>
+        <v>1.255797610679675</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>98.46954267388186</v>
+        <v>73.85215700541139</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2100,22 +2100,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1169955179898538</v>
+        <v>0.1167465385439979</v>
       </c>
       <c r="C6">
-        <v>19.48377914259484</v>
+        <v>19.34066977333732</v>
       </c>
       <c r="D6">
-        <v>18.86097914259484</v>
+        <v>18.92716977333732</v>
       </c>
       <c r="E6">
-        <v>-5.7928</v>
+        <v>-5.5835</v>
       </c>
       <c r="F6">
-        <v>0.8372000000000001</v>
+        <v>1.0465</v>
       </c>
       <c r="G6">
         <v>1.46</v>
@@ -2136,28 +2136,28 @@
         <v>3.11</v>
       </c>
       <c r="M6">
-        <v>0.04211116</v>
+        <v>0.05263895</v>
       </c>
       <c r="N6">
-        <v>3.06788884</v>
+        <v>3.05736105</v>
       </c>
       <c r="O6">
-        <v>0.7362933215999999</v>
+        <v>0.7337666519999999</v>
       </c>
       <c r="P6">
-        <v>2.3315955184</v>
+        <v>2.323594398</v>
       </c>
       <c r="Q6">
-        <v>3.6715955184</v>
+        <v>3.663594398</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1202774979060977</v>
+        <v>0.1208790932042083</v>
       </c>
       <c r="T6">
-        <v>1.255797610679675</v>
+        <v>1.265941371670625</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.85215700541139</v>
+        <v>59.08172560432912</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2182,22 +2182,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1167465385439979</v>
+        <v>0.116497559098142</v>
       </c>
       <c r="C7">
-        <v>19.34066977333732</v>
+        <v>19.1980266183812</v>
       </c>
       <c r="D7">
-        <v>18.92716977333732</v>
+        <v>18.9938266183812</v>
       </c>
       <c r="E7">
-        <v>-5.5835</v>
+        <v>-5.3742</v>
       </c>
       <c r="F7">
-        <v>1.0465</v>
+        <v>1.2558</v>
       </c>
       <c r="G7">
         <v>1.46</v>
@@ -2218,28 +2218,28 @@
         <v>3.11</v>
       </c>
       <c r="M7">
-        <v>0.05263895</v>
+        <v>0.06316674</v>
       </c>
       <c r="N7">
-        <v>3.05736105</v>
+        <v>3.04683326</v>
       </c>
       <c r="O7">
-        <v>0.7337666519999999</v>
+        <v>0.7312399823999999</v>
       </c>
       <c r="P7">
-        <v>2.323594398</v>
+        <v>2.3155932776</v>
       </c>
       <c r="Q7">
-        <v>3.663594398</v>
+        <v>3.6555932776</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1208790932042083</v>
+        <v>0.1214934884022787</v>
       </c>
       <c r="T7">
-        <v>1.265941371670625</v>
+        <v>1.276300957363511</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>59.08172560432912</v>
+        <v>49.23477133694092</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2264,22 +2264,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.116497559098142</v>
+        <v>0.1162485796522862</v>
       </c>
       <c r="C8">
-        <v>19.1980266183812</v>
+        <v>19.05585462081173</v>
       </c>
       <c r="D8">
-        <v>18.9938266183812</v>
+        <v>19.06095462081173</v>
       </c>
       <c r="E8">
-        <v>-5.3742</v>
+        <v>-5.1649</v>
       </c>
       <c r="F8">
-        <v>1.2558</v>
+        <v>1.4651</v>
       </c>
       <c r="G8">
         <v>1.46</v>
@@ -2300,28 +2300,28 @@
         <v>3.11</v>
       </c>
       <c r="M8">
-        <v>0.06316674</v>
+        <v>0.07369452999999999</v>
       </c>
       <c r="N8">
-        <v>3.04683326</v>
+        <v>3.03630547</v>
       </c>
       <c r="O8">
-        <v>0.7312399823999999</v>
+        <v>0.7287133128</v>
       </c>
       <c r="P8">
-        <v>2.3155932776</v>
+        <v>2.3075921572</v>
       </c>
       <c r="Q8">
-        <v>3.6555932776</v>
+        <v>3.6475921572</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1214934884022787</v>
+        <v>0.1221210964003077</v>
       </c>
       <c r="T8">
-        <v>1.276300957363511</v>
+        <v>1.286883329845491</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.23477133694092</v>
+        <v>42.20123257452079</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2346,22 +2346,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1162485796522862</v>
+        <v>0.1159996002064303</v>
       </c>
       <c r="C9">
-        <v>19.05585462081173</v>
+        <v>18.91415879384147</v>
       </c>
       <c r="D9">
-        <v>19.06095462081173</v>
+        <v>19.12855879384147</v>
       </c>
       <c r="E9">
-        <v>-5.164899999999999</v>
+        <v>-4.9556</v>
       </c>
       <c r="F9">
-        <v>1.4651</v>
+        <v>1.6744</v>
       </c>
       <c r="G9">
         <v>1.46</v>
@@ -2382,28 +2382,28 @@
         <v>3.11</v>
       </c>
       <c r="M9">
-        <v>0.07369452999999999</v>
+        <v>0.08422232</v>
       </c>
       <c r="N9">
-        <v>3.03630547</v>
+        <v>3.02577768</v>
       </c>
       <c r="O9">
-        <v>0.7287133128</v>
+        <v>0.7261866431999999</v>
       </c>
       <c r="P9">
-        <v>2.3075921572</v>
+        <v>2.2995910368</v>
       </c>
       <c r="Q9">
-        <v>3.6475921572</v>
+        <v>3.6395910368</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1221210964003077</v>
+        <v>0.1227623480504677</v>
       </c>
       <c r="T9">
-        <v>1.286883329845491</v>
+        <v>1.297695753903166</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.20123257452079</v>
+        <v>36.92607850270569</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2428,22 +2428,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1159996002064303</v>
+        <v>0.1157506207605744</v>
       </c>
       <c r="C10">
-        <v>18.91415879384147</v>
+        <v>18.77294422205823</v>
       </c>
       <c r="D10">
-        <v>19.12855879384147</v>
+        <v>19.19664422205823</v>
       </c>
       <c r="E10">
-        <v>-4.9556</v>
+        <v>-4.7463</v>
       </c>
       <c r="F10">
-        <v>1.6744</v>
+        <v>1.8837</v>
       </c>
       <c r="G10">
         <v>1.46</v>
@@ -2464,28 +2464,28 @@
         <v>3.11</v>
       </c>
       <c r="M10">
-        <v>0.08422232</v>
+        <v>0.09475011</v>
       </c>
       <c r="N10">
-        <v>3.02577768</v>
+        <v>3.01524989</v>
       </c>
       <c r="O10">
-        <v>0.7261866431999999</v>
+        <v>0.7236599735999999</v>
       </c>
       <c r="P10">
-        <v>2.2995910368</v>
+        <v>2.2915899164</v>
       </c>
       <c r="Q10">
-        <v>3.6395910368</v>
+        <v>3.6315899164</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1227623480504677</v>
+        <v>0.1234176931434884</v>
       </c>
       <c r="T10">
-        <v>1.297695753903166</v>
+        <v>1.308745813654416</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.92607850270569</v>
+        <v>32.82318089129395</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2510,22 +2510,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1157506207605744</v>
+        <v>0.1155016413147186</v>
       </c>
       <c r="C11">
-        <v>18.77294422205823</v>
+        <v>18.63221606269996</v>
       </c>
       <c r="D11">
-        <v>19.19664422205823</v>
+        <v>19.26521606269996</v>
       </c>
       <c r="E11">
-        <v>-4.7463</v>
+        <v>-4.537</v>
       </c>
       <c r="F11">
-        <v>1.8837</v>
+        <v>2.093</v>
       </c>
       <c r="G11">
         <v>1.46</v>
@@ -2546,28 +2546,28 @@
         <v>3.11</v>
       </c>
       <c r="M11">
-        <v>0.09475011</v>
+        <v>0.1052779</v>
       </c>
       <c r="N11">
-        <v>3.01524989</v>
+        <v>3.0047221</v>
       </c>
       <c r="O11">
-        <v>0.7236599735999999</v>
+        <v>0.721133304</v>
       </c>
       <c r="P11">
-        <v>2.2915899164</v>
+        <v>2.283588796</v>
       </c>
       <c r="Q11">
-        <v>3.6315899164</v>
+        <v>3.623588796</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1234176931434884</v>
+        <v>0.1240876014607984</v>
       </c>
       <c r="T11">
-        <v>1.308745813654416</v>
+        <v>1.320041430289028</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.82318089129395</v>
+        <v>29.54086280216456</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2592,22 +2592,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1155016413147186</v>
+        <v>0.1152526618688627</v>
       </c>
       <c r="C12">
-        <v>18.63221606269996</v>
+        <v>18.49197954695693</v>
       </c>
       <c r="D12">
-        <v>19.26521606269996</v>
+        <v>19.33427954695693</v>
       </c>
       <c r="E12">
-        <v>-4.537</v>
+        <v>-4.3277</v>
       </c>
       <c r="F12">
-        <v>2.093</v>
+        <v>2.3023</v>
       </c>
       <c r="G12">
         <v>1.46</v>
@@ -2628,28 +2628,28 @@
         <v>3.11</v>
       </c>
       <c r="M12">
-        <v>0.1052779</v>
+        <v>0.11580569</v>
       </c>
       <c r="N12">
-        <v>3.0047221</v>
+        <v>2.99419431</v>
       </c>
       <c r="O12">
-        <v>0.721133304</v>
+        <v>0.7186066343999999</v>
       </c>
       <c r="P12">
-        <v>2.283588796</v>
+        <v>2.2755876756</v>
       </c>
       <c r="Q12">
-        <v>3.623588796</v>
+        <v>3.6155876756</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1240876014607984</v>
+        <v>0.1247725638975986</v>
       </c>
       <c r="T12">
-        <v>1.320041430289028</v>
+        <v>1.331590881005317</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.54086280216456</v>
+        <v>26.8553298201496</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2674,22 +2674,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1152526618688627</v>
+        <v>0.1150036824230068</v>
       </c>
       <c r="C13">
-        <v>18.49197954695693</v>
+        <v>18.35223998130202</v>
       </c>
       <c r="D13">
-        <v>19.33427954695693</v>
+        <v>19.40383998130202</v>
       </c>
       <c r="E13">
-        <v>-4.3277</v>
+        <v>-4.118399999999999</v>
       </c>
       <c r="F13">
-        <v>2.3023</v>
+        <v>2.5116</v>
       </c>
       <c r="G13">
         <v>1.46</v>
@@ -2710,28 +2710,28 @@
         <v>3.11</v>
       </c>
       <c r="M13">
-        <v>0.11580569</v>
+        <v>0.12633348</v>
       </c>
       <c r="N13">
-        <v>2.99419431</v>
+        <v>2.98366652</v>
       </c>
       <c r="O13">
-        <v>0.7186066343999999</v>
+        <v>0.7160799647999999</v>
       </c>
       <c r="P13">
-        <v>2.2755876756</v>
+        <v>2.2675865552</v>
       </c>
       <c r="Q13">
-        <v>3.6155876756</v>
+        <v>3.6075865552</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1247725638975986</v>
+        <v>0.1254730936625078</v>
       </c>
       <c r="T13">
-        <v>1.331590881005317</v>
+        <v>1.343402819237884</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.8553298201496</v>
+        <v>24.61738566847046</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2756,22 +2756,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1150036824230068</v>
+        <v>0.114754702977151</v>
       </c>
       <c r="C14">
-        <v>18.35223998130202</v>
+        <v>18.21300274884988</v>
       </c>
       <c r="D14">
-        <v>19.40383998130202</v>
+        <v>19.47390274884988</v>
       </c>
       <c r="E14">
-        <v>-4.118399999999999</v>
+        <v>-3.9091</v>
       </c>
       <c r="F14">
-        <v>2.5116</v>
+        <v>2.7209</v>
       </c>
       <c r="G14">
         <v>1.46</v>
@@ -2792,28 +2792,28 @@
         <v>3.11</v>
       </c>
       <c r="M14">
-        <v>0.12633348</v>
+        <v>0.13686127</v>
       </c>
       <c r="N14">
-        <v>2.98366652</v>
+        <v>2.97313873</v>
       </c>
       <c r="O14">
-        <v>0.7160799647999999</v>
+        <v>0.7135532952</v>
       </c>
       <c r="P14">
-        <v>2.2675865552</v>
+        <v>2.2595854348</v>
       </c>
       <c r="Q14">
-        <v>3.6075865552</v>
+        <v>3.5995854348</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1254730936625078</v>
+        <v>0.1261897275599436</v>
       </c>
       <c r="T14">
-        <v>1.343402819237884</v>
+        <v>1.355486296280396</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.61738566847046</v>
+        <v>22.72374061704966</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2838,22 +2838,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.114754702977151</v>
+        <v>0.1145057235312951</v>
       </c>
       <c r="C15">
-        <v>18.21300274884988</v>
+        <v>18.07427331074566</v>
       </c>
       <c r="D15">
-        <v>19.47390274884988</v>
+        <v>19.54447331074566</v>
       </c>
       <c r="E15">
-        <v>-3.9091</v>
+        <v>-3.6998</v>
       </c>
       <c r="F15">
-        <v>2.7209</v>
+        <v>2.9302</v>
       </c>
       <c r="G15">
         <v>1.46</v>
@@ -2874,28 +2874,28 @@
         <v>3.11</v>
       </c>
       <c r="M15">
-        <v>0.13686127</v>
+        <v>0.14738906</v>
       </c>
       <c r="N15">
-        <v>2.97313873</v>
+        <v>2.96261094</v>
       </c>
       <c r="O15">
-        <v>0.7135532952</v>
+        <v>0.7110266256</v>
       </c>
       <c r="P15">
-        <v>2.2595854348</v>
+        <v>2.2515843144</v>
       </c>
       <c r="Q15">
-        <v>3.5995854348</v>
+        <v>3.5915843144</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1261897275599436</v>
+        <v>0.1269230273619711</v>
       </c>
       <c r="T15">
-        <v>1.355486296280396</v>
+        <v>1.367850784416919</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.72374061704966</v>
+        <v>21.1006162872604</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2920,22 +2920,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1145057235312951</v>
+        <v>0.1142567440854392</v>
       </c>
       <c r="C16">
-        <v>18.07427331074566</v>
+        <v>17.93605720758395</v>
       </c>
       <c r="D16">
-        <v>19.54447331074566</v>
+        <v>19.61555720758395</v>
       </c>
       <c r="E16">
-        <v>-3.6998</v>
+        <v>-3.490499999999999</v>
       </c>
       <c r="F16">
-        <v>2.9302</v>
+        <v>3.1395</v>
       </c>
       <c r="G16">
         <v>1.46</v>
@@ -2956,28 +2956,28 @@
         <v>3.11</v>
       </c>
       <c r="M16">
-        <v>0.14738906</v>
+        <v>0.15791685</v>
       </c>
       <c r="N16">
-        <v>2.96261094</v>
+        <v>2.95208315</v>
       </c>
       <c r="O16">
-        <v>0.7110266256</v>
+        <v>0.7084999559999999</v>
       </c>
       <c r="P16">
-        <v>2.2515843144</v>
+        <v>2.243583194</v>
       </c>
       <c r="Q16">
-        <v>3.5915843144</v>
+        <v>3.583583194</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1269230273619711</v>
+        <v>0.1276735812769874</v>
       </c>
       <c r="T16">
-        <v>1.367850784416919</v>
+        <v>1.380506201686067</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.1006162872604</v>
+        <v>19.69390853477637</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3002,22 +3002,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1142567440854392</v>
+        <v>0.1140077646395834</v>
       </c>
       <c r="C17">
-        <v>17.93605720758395</v>
+        <v>17.79836006085887</v>
       </c>
       <c r="D17">
-        <v>19.61555720758395</v>
+        <v>19.68716006085887</v>
       </c>
       <c r="E17">
-        <v>-3.4905</v>
+        <v>-3.2812</v>
       </c>
       <c r="F17">
-        <v>3.1395</v>
+        <v>3.3488</v>
       </c>
       <c r="G17">
         <v>1.46</v>
@@ -3038,28 +3038,28 @@
         <v>3.11</v>
       </c>
       <c r="M17">
-        <v>0.15791685</v>
+        <v>0.16844464</v>
       </c>
       <c r="N17">
-        <v>2.95208315</v>
+        <v>2.94155536</v>
       </c>
       <c r="O17">
-        <v>0.7084999559999999</v>
+        <v>0.7059732863999999</v>
       </c>
       <c r="P17">
-        <v>2.243583194</v>
+        <v>2.2355820736</v>
       </c>
       <c r="Q17">
-        <v>3.583583194</v>
+        <v>3.5755820736</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1276735812769874</v>
+        <v>0.1284420055233136</v>
       </c>
       <c r="T17">
-        <v>1.380506201686067</v>
+        <v>1.393462938414003</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.69390853477637</v>
+        <v>18.46303925135285</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3084,22 +3084,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1140077646395834</v>
+        <v>0.1137587851937275</v>
       </c>
       <c r="C18">
-        <v>17.79836006085887</v>
+        <v>17.66118757444604</v>
       </c>
       <c r="D18">
-        <v>19.68716006085887</v>
+        <v>19.75928757444604</v>
       </c>
       <c r="E18">
-        <v>-3.2812</v>
+        <v>-3.0719</v>
       </c>
       <c r="F18">
-        <v>3.3488</v>
+        <v>3.5581</v>
       </c>
       <c r="G18">
         <v>1.46</v>
@@ -3120,28 +3120,28 @@
         <v>3.11</v>
       </c>
       <c r="M18">
-        <v>0.16844464</v>
+        <v>0.17897243</v>
       </c>
       <c r="N18">
-        <v>2.94155536</v>
+        <v>2.93102757</v>
       </c>
       <c r="O18">
-        <v>0.7059732863999999</v>
+        <v>0.7034466168</v>
       </c>
       <c r="P18">
-        <v>2.2355820736</v>
+        <v>2.2275809532</v>
       </c>
       <c r="Q18">
-        <v>3.5755820736</v>
+        <v>3.5675809532</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1284420055233136</v>
+        <v>0.1292289460165392</v>
       </c>
       <c r="T18">
-        <v>1.393462938414003</v>
+        <v>1.406731885665505</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.46303925135285</v>
+        <v>17.37697811892033</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3166,22 +3166,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1137587851937275</v>
+        <v>0.1135098057478716</v>
       </c>
       <c r="C19">
-        <v>17.66118757444604</v>
+        <v>17.52454553611723</v>
       </c>
       <c r="D19">
-        <v>19.75928757444604</v>
+        <v>19.83194553611723</v>
       </c>
       <c r="E19">
-        <v>-3.0719</v>
+        <v>-2.8626</v>
       </c>
       <c r="F19">
-        <v>3.5581</v>
+        <v>3.7674</v>
       </c>
       <c r="G19">
         <v>1.46</v>
@@ -3202,28 +3202,28 @@
         <v>3.11</v>
       </c>
       <c r="M19">
-        <v>0.17897243</v>
+        <v>0.18950022</v>
       </c>
       <c r="N19">
-        <v>2.93102757</v>
+        <v>2.92049978</v>
       </c>
       <c r="O19">
-        <v>0.7034466168</v>
+        <v>0.7009199471999999</v>
       </c>
       <c r="P19">
-        <v>2.2275809532</v>
+        <v>2.2195798328</v>
       </c>
       <c r="Q19">
-        <v>3.5675809532</v>
+        <v>3.5595798328</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1292289460165392</v>
+        <v>0.1300350801803313</v>
       </c>
       <c r="T19">
-        <v>1.406731885665505</v>
+        <v>1.420324465776799</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.37697811892033</v>
+        <v>16.41159044564698</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3248,22 +3248,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1135098057478717</v>
+        <v>0.1132608263020158</v>
       </c>
       <c r="C20">
-        <v>17.52454553611723</v>
+        <v>17.3884398190885</v>
       </c>
       <c r="D20">
-        <v>19.83194553611722</v>
+        <v>19.9051398190885</v>
       </c>
       <c r="E20">
-        <v>-2.8626</v>
+        <v>-2.6533</v>
       </c>
       <c r="F20">
-        <v>3.7674</v>
+        <v>3.9767</v>
       </c>
       <c r="G20">
         <v>1.46</v>
@@ -3284,28 +3284,28 @@
         <v>3.11</v>
       </c>
       <c r="M20">
-        <v>0.18950022</v>
+        <v>0.20002801</v>
       </c>
       <c r="N20">
-        <v>2.92049978</v>
+        <v>2.90997199</v>
       </c>
       <c r="O20">
-        <v>0.7009199471999999</v>
+        <v>0.6983932775999999</v>
       </c>
       <c r="P20">
-        <v>2.2195798328</v>
+        <v>2.2115787124</v>
       </c>
       <c r="Q20">
-        <v>3.5595798328</v>
+        <v>3.5515787124</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1300350801803313</v>
+        <v>0.1308611188913775</v>
       </c>
       <c r="T20">
-        <v>1.420324465776799</v>
+        <v>1.434252665150101</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.41159044564698</v>
+        <v>15.54782252745503</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3330,22 +3330,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1132608263020158</v>
+        <v>0.1130118468561599</v>
       </c>
       <c r="C21">
-        <v>17.3884398190885</v>
+        <v>17.25287638360289</v>
       </c>
       <c r="D21">
-        <v>19.9051398190885</v>
+        <v>19.97887638360289</v>
       </c>
       <c r="E21">
-        <v>-2.6533</v>
+        <v>-2.444</v>
       </c>
       <c r="F21">
-        <v>3.9767</v>
+        <v>4.186</v>
       </c>
       <c r="G21">
         <v>1.46</v>
@@ -3366,28 +3366,28 @@
         <v>3.11</v>
       </c>
       <c r="M21">
-        <v>0.20002801</v>
+        <v>0.2105558</v>
       </c>
       <c r="N21">
-        <v>2.90997199</v>
+        <v>2.8994442</v>
       </c>
       <c r="O21">
-        <v>0.6983932775999999</v>
+        <v>0.695866608</v>
       </c>
       <c r="P21">
-        <v>2.2115787124</v>
+        <v>2.203577592</v>
       </c>
       <c r="Q21">
-        <v>3.5515787124</v>
+        <v>3.543577592000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1308611188913775</v>
+        <v>0.1317078085701999</v>
       </c>
       <c r="T21">
-        <v>1.434252665150101</v>
+        <v>1.448529069507735</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.54782252745503</v>
+        <v>14.77043140108228</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3412,22 +3412,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1130118468561599</v>
+        <v>0.1127628674103041</v>
       </c>
       <c r="C22">
-        <v>17.25287638360289</v>
+        <v>17.11786127854822</v>
       </c>
       <c r="D22">
-        <v>19.97887638360289</v>
+        <v>20.05316127854822</v>
       </c>
       <c r="E22">
-        <v>-2.444</v>
+        <v>-2.234699999999999</v>
       </c>
       <c r="F22">
-        <v>4.186</v>
+        <v>4.395300000000001</v>
       </c>
       <c r="G22">
         <v>1.46</v>
@@ -3448,28 +3448,28 @@
         <v>3.11</v>
       </c>
       <c r="M22">
-        <v>0.2105558</v>
+        <v>0.22108359</v>
       </c>
       <c r="N22">
-        <v>2.8994442</v>
+        <v>2.88891641</v>
       </c>
       <c r="O22">
-        <v>0.695866608</v>
+        <v>0.6933399384</v>
       </c>
       <c r="P22">
-        <v>2.203577592</v>
+        <v>2.1955764716</v>
       </c>
       <c r="Q22">
-        <v>3.543577592000001</v>
+        <v>3.5355764716</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1317078085701999</v>
+        <v>0.1325759334307646</v>
       </c>
       <c r="T22">
-        <v>1.448529069507735</v>
+        <v>1.46316690182379</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.77043140108228</v>
+        <v>14.06707752484026</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3494,22 +3494,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1127628674103041</v>
+        <v>0.1125138879644482</v>
       </c>
       <c r="C23">
-        <v>17.11786127854822</v>
+        <v>16.98340064311129</v>
       </c>
       <c r="D23">
-        <v>20.05316127854822</v>
+        <v>20.12800064311129</v>
       </c>
       <c r="E23">
-        <v>-2.2347</v>
+        <v>-2.0254</v>
       </c>
       <c r="F23">
-        <v>4.3953</v>
+        <v>4.6046</v>
       </c>
       <c r="G23">
         <v>1.46</v>
@@ -3530,28 +3530,28 @@
         <v>3.11</v>
       </c>
       <c r="M23">
-        <v>0.22108359</v>
+        <v>0.23161138</v>
       </c>
       <c r="N23">
-        <v>2.88891641</v>
+        <v>2.87838862</v>
       </c>
       <c r="O23">
-        <v>0.6933399384</v>
+        <v>0.6908132687999999</v>
       </c>
       <c r="P23">
-        <v>2.1955764716</v>
+        <v>2.1875753512</v>
       </c>
       <c r="Q23">
-        <v>3.5355764716</v>
+        <v>3.5275753512</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1325759334307646</v>
+        <v>0.1334663179031387</v>
       </c>
       <c r="T23">
-        <v>1.46316690182379</v>
+        <v>1.47818006317359</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.06707752484027</v>
+        <v>13.4276649100748</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3576,22 +3576,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1125138879644482</v>
+        <v>0.1125271085185923</v>
       </c>
       <c r="C24">
-        <v>16.98340064311129</v>
+        <v>16.77011270884854</v>
       </c>
       <c r="D24">
-        <v>20.12800064311129</v>
+        <v>20.12401270884854</v>
       </c>
       <c r="E24">
-        <v>-2.0254</v>
+        <v>-1.8161</v>
       </c>
       <c r="F24">
-        <v>4.6046</v>
+        <v>4.8139</v>
       </c>
       <c r="G24">
         <v>1.46</v>
@@ -3612,45 +3612,45 @@
         <v>3.11</v>
       </c>
       <c r="M24">
-        <v>0.23161138</v>
+        <v>0.24936002</v>
       </c>
       <c r="N24">
-        <v>2.87838862</v>
+        <v>2.86063998</v>
       </c>
       <c r="O24">
-        <v>0.6908132687999999</v>
+        <v>0.6865535951999999</v>
       </c>
       <c r="P24">
-        <v>2.1875753512</v>
+        <v>2.1740863848</v>
       </c>
       <c r="Q24">
-        <v>3.5275753512</v>
+        <v>3.5140863848</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1334663179031387</v>
+        <v>0.1343798292449251</v>
       </c>
       <c r="T24">
-        <v>1.47818006317359</v>
+        <v>1.493583176766242</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.4276649100748</v>
+        <v>12.47192713571325</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3658,22 +3658,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1125271085185923</v>
+        <v>0.1122895290727365</v>
       </c>
       <c r="C25">
-        <v>16.77011270884854</v>
+        <v>16.63271954672875</v>
       </c>
       <c r="D25">
-        <v>20.12401270884854</v>
+        <v>20.19591954672875</v>
       </c>
       <c r="E25">
-        <v>-1.8161</v>
+        <v>-1.6068</v>
       </c>
       <c r="F25">
-        <v>4.8139</v>
+        <v>5.0232</v>
       </c>
       <c r="G25">
         <v>1.46</v>
@@ -3694,28 +3694,28 @@
         <v>3.11</v>
       </c>
       <c r="M25">
-        <v>0.24936002</v>
+        <v>0.26020176</v>
       </c>
       <c r="N25">
-        <v>2.86063998</v>
+        <v>2.84979824</v>
       </c>
       <c r="O25">
-        <v>0.6865535951999999</v>
+        <v>0.6839515775999999</v>
       </c>
       <c r="P25">
-        <v>2.1740863848</v>
+        <v>2.1658466624</v>
       </c>
       <c r="Q25">
-        <v>3.5140863848</v>
+        <v>3.5058466624</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1343798292449251</v>
+        <v>0.1353173803588638</v>
       </c>
       <c r="T25">
-        <v>1.493583176766242</v>
+        <v>1.509391635453438</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.47192713571325</v>
+        <v>11.95226350505853</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3740,22 +3740,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1122895290727365</v>
+        <v>0.1120519496268806</v>
       </c>
       <c r="C26">
-        <v>16.63271954672875</v>
+        <v>16.49584210035146</v>
       </c>
       <c r="D26">
-        <v>20.19591954672875</v>
+        <v>20.26834210035146</v>
       </c>
       <c r="E26">
-        <v>-1.6068</v>
+        <v>-1.3975</v>
       </c>
       <c r="F26">
-        <v>5.0232</v>
+        <v>5.2325</v>
       </c>
       <c r="G26">
         <v>1.46</v>
@@ -3776,28 +3776,28 @@
         <v>3.11</v>
       </c>
       <c r="M26">
-        <v>0.26020176</v>
+        <v>0.2710435</v>
       </c>
       <c r="N26">
-        <v>2.84979824</v>
+        <v>2.8389565</v>
       </c>
       <c r="O26">
-        <v>0.6839515775999999</v>
+        <v>0.68134956</v>
       </c>
       <c r="P26">
-        <v>2.1658466624</v>
+        <v>2.15760694</v>
       </c>
       <c r="Q26">
-        <v>3.5058466624</v>
+        <v>3.49760694</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1353173803588638</v>
+        <v>0.1362799328358408</v>
       </c>
       <c r="T26">
-        <v>1.509391635453438</v>
+        <v>1.525621653038959</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.95226350505853</v>
+        <v>11.4741729648562</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3822,22 +3822,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1120519496268806</v>
+        <v>0.1118143701810247</v>
       </c>
       <c r="C27">
-        <v>16.49584210035146</v>
+        <v>16.35948593775252</v>
       </c>
       <c r="D27">
-        <v>20.26834210035146</v>
+        <v>20.34128593775252</v>
       </c>
       <c r="E27">
-        <v>-1.3975</v>
+        <v>-1.1882</v>
       </c>
       <c r="F27">
-        <v>5.2325</v>
+        <v>5.4418</v>
       </c>
       <c r="G27">
         <v>1.46</v>
@@ -3858,28 +3858,28 @@
         <v>3.11</v>
       </c>
       <c r="M27">
-        <v>0.2710435</v>
+        <v>0.28188524</v>
       </c>
       <c r="N27">
-        <v>2.8389565</v>
+        <v>2.82811476</v>
       </c>
       <c r="O27">
-        <v>0.68134956</v>
+        <v>0.6787475424</v>
       </c>
       <c r="P27">
-        <v>2.15760694</v>
+        <v>2.1493672176</v>
       </c>
       <c r="Q27">
-        <v>3.49760694</v>
+        <v>3.4893672176</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1362799328358408</v>
+        <v>0.137268500244628</v>
       </c>
       <c r="T27">
-        <v>1.525621653038959</v>
+        <v>1.542290319748412</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.4741729648562</v>
+        <v>11.03285862005403</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3904,22 +3904,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1118143701810247</v>
+        <v>0.1115767907351689</v>
       </c>
       <c r="C28">
-        <v>16.35948593775252</v>
+        <v>16.22365670741266</v>
       </c>
       <c r="D28">
-        <v>20.34128593775252</v>
+        <v>20.41475670741266</v>
       </c>
       <c r="E28">
-        <v>-1.1882</v>
+        <v>-0.9788999999999994</v>
       </c>
       <c r="F28">
-        <v>5.4418</v>
+        <v>5.6511</v>
       </c>
       <c r="G28">
         <v>1.46</v>
@@ -3940,28 +3940,28 @@
         <v>3.11</v>
       </c>
       <c r="M28">
-        <v>0.28188524</v>
+        <v>0.29272698</v>
       </c>
       <c r="N28">
-        <v>2.82811476</v>
+        <v>2.81727302</v>
       </c>
       <c r="O28">
-        <v>0.6787475424</v>
+        <v>0.6761455248</v>
       </c>
       <c r="P28">
-        <v>2.1493672176</v>
+        <v>2.1411274952</v>
       </c>
       <c r="Q28">
-        <v>3.4893672176</v>
+        <v>3.4811274952</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.137268500244628</v>
+        <v>0.1382841516920121</v>
       </c>
       <c r="T28">
-        <v>1.542290319748412</v>
+        <v>1.559415662258125</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.03285862005403</v>
+        <v>10.6242342267187</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3986,22 +3986,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1115767907351689</v>
+        <v>0.111339211289313</v>
       </c>
       <c r="C29">
-        <v>16.22365670741266</v>
+        <v>16.0883601397155</v>
       </c>
       <c r="D29">
-        <v>20.41475670741266</v>
+        <v>20.4887601397155</v>
       </c>
       <c r="E29">
-        <v>-0.9788999999999994</v>
+        <v>-0.7695999999999996</v>
       </c>
       <c r="F29">
-        <v>5.6511</v>
+        <v>5.8604</v>
       </c>
       <c r="G29">
         <v>1.46</v>
@@ -4022,28 +4022,28 @@
         <v>3.11</v>
       </c>
       <c r="M29">
-        <v>0.29272698</v>
+        <v>0.30356872</v>
       </c>
       <c r="N29">
-        <v>2.81727302</v>
+        <v>2.80643128</v>
       </c>
       <c r="O29">
-        <v>0.6761455248</v>
+        <v>0.6735435072</v>
       </c>
       <c r="P29">
-        <v>2.1411274952</v>
+        <v>2.1328877728</v>
       </c>
       <c r="Q29">
-        <v>3.4811274952</v>
+        <v>3.4728877728</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1382841516920121</v>
+        <v>0.1393280156796014</v>
       </c>
       <c r="T29">
-        <v>1.559415662258125</v>
+        <v>1.577016708726441</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.6242342267187</v>
+        <v>10.24479729005017</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4068,22 +4068,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.111339211289313</v>
+        <v>0.1111016318434571</v>
       </c>
       <c r="C30">
-        <v>16.0883601397155</v>
+        <v>15.95360204843741</v>
       </c>
       <c r="D30">
-        <v>20.4887601397155</v>
+        <v>20.56330204843741</v>
       </c>
       <c r="E30">
-        <v>-0.7695999999999996</v>
+        <v>-0.5602999999999989</v>
       </c>
       <c r="F30">
-        <v>5.8604</v>
+        <v>6.069700000000001</v>
       </c>
       <c r="G30">
         <v>1.46</v>
@@ -4104,28 +4104,28 @@
         <v>3.11</v>
       </c>
       <c r="M30">
-        <v>0.30356872</v>
+        <v>0.3144104600000001</v>
       </c>
       <c r="N30">
-        <v>2.80643128</v>
+        <v>2.79558954</v>
       </c>
       <c r="O30">
-        <v>0.6735435072</v>
+        <v>0.6709414896</v>
       </c>
       <c r="P30">
-        <v>2.1328877728</v>
+        <v>2.1246480504</v>
       </c>
       <c r="Q30">
-        <v>3.4728877728</v>
+        <v>3.4646480504</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1393280156796014</v>
+        <v>0.1404012842865593</v>
       </c>
       <c r="T30">
-        <v>1.577016708726441</v>
+        <v>1.595113559320626</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.24479729005017</v>
+        <v>9.891528417979476</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4150,22 +4150,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1111016318434571</v>
+        <v>0.1112516523976013</v>
       </c>
       <c r="C31">
-        <v>15.95360204843741</v>
+        <v>15.69716927401027</v>
       </c>
       <c r="D31">
-        <v>20.56330204843741</v>
+        <v>20.51616927401027</v>
       </c>
       <c r="E31">
-        <v>-0.5603000000000007</v>
+        <v>-0.351</v>
       </c>
       <c r="F31">
-        <v>6.069699999999999</v>
+        <v>6.279</v>
       </c>
       <c r="G31">
         <v>1.46</v>
@@ -4186,45 +4186,45 @@
         <v>3.11</v>
       </c>
       <c r="M31">
-        <v>0.3144104599999999</v>
+        <v>0.3359265</v>
       </c>
       <c r="N31">
-        <v>2.79558954</v>
+        <v>2.7740735</v>
       </c>
       <c r="O31">
-        <v>0.6709414896</v>
+        <v>0.6657776399999999</v>
       </c>
       <c r="P31">
-        <v>2.1246480504</v>
+        <v>2.10829586</v>
       </c>
       <c r="Q31">
-        <v>3.4646480504</v>
+        <v>3.44829586</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1404012842865593</v>
+        <v>0.1415052177108589</v>
       </c>
       <c r="T31">
-        <v>1.595113559320626</v>
+        <v>1.613727462788929</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.89152841797948</v>
+        <v>9.257977563544408</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4232,22 +4232,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1112516523976013</v>
+        <v>0.1110269929517454</v>
       </c>
       <c r="C32">
-        <v>15.69716927401027</v>
+        <v>15.55853252263794</v>
       </c>
       <c r="D32">
-        <v>20.51616927401027</v>
+        <v>20.58683252263794</v>
       </c>
       <c r="E32">
-        <v>-0.351</v>
+        <v>-0.1417000000000002</v>
       </c>
       <c r="F32">
-        <v>6.279</v>
+        <v>6.4883</v>
       </c>
       <c r="G32">
         <v>1.46</v>
@@ -4268,28 +4268,28 @@
         <v>3.11</v>
       </c>
       <c r="M32">
-        <v>0.3359265</v>
+        <v>0.34712405</v>
       </c>
       <c r="N32">
-        <v>2.7740735</v>
+        <v>2.76287595</v>
       </c>
       <c r="O32">
-        <v>0.6657776399999999</v>
+        <v>0.6630902279999999</v>
       </c>
       <c r="P32">
-        <v>2.10829586</v>
+        <v>2.099785722</v>
       </c>
       <c r="Q32">
-        <v>3.44829586</v>
+        <v>3.439785722</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1415052177108589</v>
+        <v>0.1426411492054281</v>
       </c>
       <c r="T32">
-        <v>1.613727462788929</v>
+        <v>1.632880899691096</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.257977563544408</v>
+        <v>8.959333126010716</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4314,22 +4314,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1110269929517454</v>
+        <v>0.1108023335058895</v>
       </c>
       <c r="C33">
-        <v>15.55853252263794</v>
+        <v>15.42038422038499</v>
       </c>
       <c r="D33">
-        <v>20.58683252263794</v>
+        <v>20.65798422038499</v>
       </c>
       <c r="E33">
-        <v>-0.1417000000000002</v>
+        <v>0.06760000000000055</v>
       </c>
       <c r="F33">
-        <v>6.4883</v>
+        <v>6.6976</v>
       </c>
       <c r="G33">
         <v>1.46</v>
@@ -4350,28 +4350,28 @@
         <v>3.11</v>
       </c>
       <c r="M33">
-        <v>0.34712405</v>
+        <v>0.3583216</v>
       </c>
       <c r="N33">
-        <v>2.76287595</v>
+        <v>2.7516784</v>
       </c>
       <c r="O33">
-        <v>0.6630902279999999</v>
+        <v>0.6604028159999999</v>
       </c>
       <c r="P33">
-        <v>2.099785722</v>
+        <v>2.091275584</v>
       </c>
       <c r="Q33">
-        <v>3.439785722</v>
+        <v>3.431275584</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1426411492054281</v>
+        <v>0.1438104904498375</v>
       </c>
       <c r="T33">
-        <v>1.632880899691096</v>
+        <v>1.652597672972739</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.959333126010716</v>
+        <v>8.67935396582288</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4396,22 +4396,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1108023335058895</v>
+        <v>0.1105776740600337</v>
       </c>
       <c r="C34">
-        <v>15.42038422038499</v>
+        <v>15.28272944931292</v>
       </c>
       <c r="D34">
-        <v>20.65798422038499</v>
+        <v>20.72962944931292</v>
       </c>
       <c r="E34">
-        <v>0.06760000000000055</v>
+        <v>0.2769000000000004</v>
       </c>
       <c r="F34">
-        <v>6.6976</v>
+        <v>6.9069</v>
       </c>
       <c r="G34">
         <v>1.46</v>
@@ -4432,28 +4432,28 @@
         <v>3.11</v>
       </c>
       <c r="M34">
-        <v>0.3583216</v>
+        <v>0.36951915</v>
       </c>
       <c r="N34">
-        <v>2.7516784</v>
+        <v>2.74048085</v>
       </c>
       <c r="O34">
-        <v>0.6604028159999999</v>
+        <v>0.6577154039999999</v>
       </c>
       <c r="P34">
-        <v>2.091275584</v>
+        <v>2.082765446</v>
       </c>
       <c r="Q34">
-        <v>3.431275584</v>
+        <v>3.422765446</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1438104904498375</v>
+        <v>0.1450147374030353</v>
       </c>
       <c r="T34">
-        <v>1.652597672972739</v>
+        <v>1.672903006650849</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.67935396582288</v>
+        <v>8.416343239585824</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4478,22 +4478,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1105776740600337</v>
+        <v>0.1103530146141778</v>
       </c>
       <c r="C35">
-        <v>15.28272944931292</v>
+        <v>15.14557336223031</v>
       </c>
       <c r="D35">
-        <v>20.72962944931292</v>
+        <v>20.80177336223031</v>
       </c>
       <c r="E35">
-        <v>0.2769000000000004</v>
+        <v>0.4862000000000002</v>
       </c>
       <c r="F35">
-        <v>6.9069</v>
+        <v>7.1162</v>
       </c>
       <c r="G35">
         <v>1.46</v>
@@ -4514,28 +4514,28 @@
         <v>3.11</v>
       </c>
       <c r="M35">
-        <v>0.36951915</v>
+        <v>0.3807167</v>
       </c>
       <c r="N35">
-        <v>2.74048085</v>
+        <v>2.7292833</v>
       </c>
       <c r="O35">
-        <v>0.6577154039999999</v>
+        <v>0.6550279919999998</v>
       </c>
       <c r="P35">
-        <v>2.082765446</v>
+        <v>2.074255308</v>
       </c>
       <c r="Q35">
-        <v>3.422765446</v>
+        <v>3.414255308</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1450147374030353</v>
+        <v>0.1462554766881482</v>
       </c>
       <c r="T35">
-        <v>1.672903006650849</v>
+        <v>1.69382365347072</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.416343239585824</v>
+        <v>8.168803732539182</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4560,22 +4560,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1103530146141778</v>
+        <v>0.1101283551683219</v>
       </c>
       <c r="C36">
-        <v>15.14557336223031</v>
+        <v>15.00892118392807</v>
       </c>
       <c r="D36">
-        <v>20.80177336223031</v>
+        <v>20.87442118392807</v>
       </c>
       <c r="E36">
-        <v>0.4862000000000002</v>
+        <v>0.6955000000000009</v>
       </c>
       <c r="F36">
-        <v>7.1162</v>
+        <v>7.325500000000001</v>
       </c>
       <c r="G36">
         <v>1.46</v>
@@ -4596,28 +4596,28 @@
         <v>3.11</v>
       </c>
       <c r="M36">
-        <v>0.3807167</v>
+        <v>0.39191425</v>
       </c>
       <c r="N36">
-        <v>2.7292833</v>
+        <v>2.71808575</v>
       </c>
       <c r="O36">
-        <v>0.6550279919999998</v>
+        <v>0.6523405799999999</v>
       </c>
       <c r="P36">
-        <v>2.074255308</v>
+        <v>2.06574517</v>
       </c>
       <c r="Q36">
-        <v>3.414255308</v>
+        <v>3.40574517</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1462554766881482</v>
+        <v>0.1475343925666491</v>
       </c>
       <c r="T36">
-        <v>1.69382365347072</v>
+        <v>1.715388012500433</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.168803732539182</v>
+        <v>7.935409340180919</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4642,22 +4642,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1101283551683219</v>
+        <v>0.1099036957224661</v>
       </c>
       <c r="C37">
-        <v>15.00892118392807</v>
+        <v>14.87277821244084</v>
       </c>
       <c r="D37">
-        <v>20.87442118392807</v>
+        <v>20.94757821244084</v>
       </c>
       <c r="E37">
-        <v>0.6955000000000009</v>
+        <v>0.9048000000000007</v>
       </c>
       <c r="F37">
-        <v>7.325500000000001</v>
+        <v>7.534800000000001</v>
       </c>
       <c r="G37">
         <v>1.46</v>
@@ -4678,28 +4678,28 @@
         <v>3.11</v>
       </c>
       <c r="M37">
-        <v>0.39191425</v>
+        <v>0.4031118</v>
       </c>
       <c r="N37">
-        <v>2.71808575</v>
+        <v>2.7068882</v>
       </c>
       <c r="O37">
-        <v>0.6523405799999999</v>
+        <v>0.6496531679999999</v>
       </c>
       <c r="P37">
-        <v>2.06574517</v>
+        <v>2.057235032</v>
       </c>
       <c r="Q37">
-        <v>3.40574517</v>
+        <v>3.397235032</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1475343925666491</v>
+        <v>0.1488532745663532</v>
       </c>
       <c r="T37">
-        <v>1.715388012500433</v>
+        <v>1.737626257749825</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.935409340180919</v>
+        <v>7.714981302953671</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4724,22 +4724,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1099036957224661</v>
+        <v>0.1099039962766102</v>
       </c>
       <c r="C38">
-        <v>14.87277821244084</v>
+        <v>14.66337999888464</v>
       </c>
       <c r="D38">
-        <v>20.94757821244084</v>
+        <v>20.94747999888464</v>
       </c>
       <c r="E38">
-        <v>0.9047999999999998</v>
+        <v>1.1141</v>
       </c>
       <c r="F38">
-        <v>7.5348</v>
+        <v>7.7441</v>
       </c>
       <c r="G38">
         <v>1.46</v>
@@ -4760,45 +4760,45 @@
         <v>3.11</v>
       </c>
       <c r="M38">
-        <v>0.4031118</v>
+        <v>0.42050463</v>
       </c>
       <c r="N38">
-        <v>2.7068882</v>
+        <v>2.68949537</v>
       </c>
       <c r="O38">
-        <v>0.6496531679999999</v>
+        <v>0.6454788887999999</v>
       </c>
       <c r="P38">
-        <v>2.057235032</v>
+        <v>2.0440164812</v>
       </c>
       <c r="Q38">
-        <v>3.397235032</v>
+        <v>3.3840164812</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1488532745663532</v>
+        <v>0.1502140258358892</v>
       </c>
       <c r="T38">
-        <v>1.737626257749825</v>
+        <v>1.760570479038879</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.714981302953672</v>
+        <v>7.395875760036221</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4806,22 +4806,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1099039962766102</v>
+        <v>0.1096854168307543</v>
       </c>
       <c r="C39">
-        <v>14.66337999888464</v>
+        <v>14.52575032362186</v>
       </c>
       <c r="D39">
-        <v>20.94747999888464</v>
+        <v>21.01915032362186</v>
       </c>
       <c r="E39">
-        <v>1.1141</v>
+        <v>1.3234</v>
       </c>
       <c r="F39">
-        <v>7.7441</v>
+        <v>7.9534</v>
       </c>
       <c r="G39">
         <v>1.46</v>
@@ -4842,28 +4842,28 @@
         <v>3.11</v>
       </c>
       <c r="M39">
-        <v>0.42050463</v>
+        <v>0.43186962</v>
       </c>
       <c r="N39">
-        <v>2.68949537</v>
+        <v>2.67813038</v>
       </c>
       <c r="O39">
-        <v>0.6454788887999999</v>
+        <v>0.6427512912</v>
       </c>
       <c r="P39">
-        <v>2.0440164812</v>
+        <v>2.0353790888</v>
       </c>
       <c r="Q39">
-        <v>3.3840164812</v>
+        <v>3.3753790888</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1502140258358892</v>
+        <v>0.1516186723076683</v>
       </c>
       <c r="T39">
-        <v>1.760570479038879</v>
+        <v>1.784254836498549</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.395875760036221</v>
+        <v>7.201247450561583</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4888,22 +4888,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1096854168307543</v>
+        <v>0.1094668373848985</v>
       </c>
       <c r="C40">
-        <v>14.52575032362186</v>
+        <v>14.38861276200911</v>
       </c>
       <c r="D40">
-        <v>21.01915032362186</v>
+        <v>21.09131276200911</v>
       </c>
       <c r="E40">
-        <v>1.3234</v>
+        <v>1.532700000000001</v>
       </c>
       <c r="F40">
-        <v>7.9534</v>
+        <v>8.162700000000001</v>
       </c>
       <c r="G40">
         <v>1.46</v>
@@ -4924,28 +4924,28 @@
         <v>3.11</v>
       </c>
       <c r="M40">
-        <v>0.43186962</v>
+        <v>0.4432346100000001</v>
       </c>
       <c r="N40">
-        <v>2.67813038</v>
+        <v>2.66676539</v>
       </c>
       <c r="O40">
-        <v>0.6427512912</v>
+        <v>0.6400236935999999</v>
       </c>
       <c r="P40">
-        <v>2.0353790888</v>
+        <v>2.0267416964</v>
       </c>
       <c r="Q40">
-        <v>3.3753790888</v>
+        <v>3.3667416964</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1516186723076683</v>
+        <v>0.1530693727621286</v>
       </c>
       <c r="T40">
-        <v>1.784254836498549</v>
+        <v>1.808715730268371</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.201247450561583</v>
+        <v>7.016600080034362</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4970,22 +4970,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1094668373848985</v>
+        <v>0.1092482579390426</v>
       </c>
       <c r="C41">
-        <v>14.38861276200911</v>
+        <v>14.25197240004553</v>
       </c>
       <c r="D41">
-        <v>21.09131276200911</v>
+        <v>21.16397240004553</v>
       </c>
       <c r="E41">
-        <v>1.532700000000001</v>
+        <v>1.742</v>
       </c>
       <c r="F41">
-        <v>8.162700000000001</v>
+        <v>8.372</v>
       </c>
       <c r="G41">
         <v>1.46</v>
@@ -5006,28 +5006,28 @@
         <v>3.11</v>
       </c>
       <c r="M41">
-        <v>0.4432346100000001</v>
+        <v>0.4545996</v>
       </c>
       <c r="N41">
-        <v>2.66676539</v>
+        <v>2.6554004</v>
       </c>
       <c r="O41">
-        <v>0.6400236935999999</v>
+        <v>0.6372960959999999</v>
       </c>
       <c r="P41">
-        <v>2.0267416964</v>
+        <v>2.018104304</v>
       </c>
       <c r="Q41">
-        <v>3.3667416964</v>
+        <v>3.358104304</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1530693727621286</v>
+        <v>0.1545684298984044</v>
       </c>
       <c r="T41">
-        <v>1.808715730268371</v>
+        <v>1.833991987163855</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.016600080034362</v>
+        <v>6.841185078033504</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5052,22 +5052,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1092482579390426</v>
+        <v>0.1090296784931867</v>
       </c>
       <c r="C42">
-        <v>14.25197240004553</v>
+        <v>14.11583439405772</v>
       </c>
       <c r="D42">
-        <v>21.16397240004553</v>
+        <v>21.23713439405772</v>
       </c>
       <c r="E42">
-        <v>1.742</v>
+        <v>1.951300000000001</v>
       </c>
       <c r="F42">
-        <v>8.372</v>
+        <v>8.581300000000001</v>
       </c>
       <c r="G42">
         <v>1.46</v>
@@ -5088,28 +5088,28 @@
         <v>3.11</v>
       </c>
       <c r="M42">
-        <v>0.4545996</v>
+        <v>0.4659645900000001</v>
       </c>
       <c r="N42">
-        <v>2.6554004</v>
+        <v>2.64403541</v>
       </c>
       <c r="O42">
-        <v>0.6372960959999999</v>
+        <v>0.6345684984</v>
       </c>
       <c r="P42">
-        <v>2.018104304</v>
+        <v>2.0094669116</v>
       </c>
       <c r="Q42">
-        <v>3.358104304</v>
+        <v>3.3494669116</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1545684298984044</v>
+        <v>0.156118302530825</v>
       </c>
       <c r="T42">
-        <v>1.833991987163855</v>
+        <v>1.860125066326981</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.841185078033504</v>
+        <v>6.67432690539854</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5134,22 +5134,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1090296784931867</v>
+        <v>0.1088110990473309</v>
       </c>
       <c r="C43">
-        <v>14.11583439405772</v>
+        <v>13.98020397191943</v>
       </c>
       <c r="D43">
-        <v>21.23713439405772</v>
+        <v>21.31080397191943</v>
       </c>
       <c r="E43">
-        <v>1.951300000000001</v>
+        <v>2.160600000000001</v>
       </c>
       <c r="F43">
-        <v>8.581300000000001</v>
+        <v>8.790600000000001</v>
       </c>
       <c r="G43">
         <v>1.46</v>
@@ -5170,28 +5170,28 @@
         <v>3.11</v>
       </c>
       <c r="M43">
-        <v>0.4659645900000001</v>
+        <v>0.4773295800000001</v>
       </c>
       <c r="N43">
-        <v>2.64403541</v>
+        <v>2.63267042</v>
       </c>
       <c r="O43">
-        <v>0.6345684984</v>
+        <v>0.6318409007999999</v>
       </c>
       <c r="P43">
-        <v>2.0094669116</v>
+        <v>2.0008295192</v>
       </c>
       <c r="Q43">
-        <v>3.3494669116</v>
+        <v>3.3408295192</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.156118302530825</v>
+        <v>0.1577216190471222</v>
       </c>
       <c r="T43">
-        <v>1.860125066326981</v>
+        <v>1.887159286150906</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.67432690539854</v>
+        <v>6.515414360031907</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5216,22 +5216,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1088110990473309</v>
+        <v>0.108592519601475</v>
       </c>
       <c r="C44">
-        <v>13.98020397191943</v>
+        <v>13.84508643429694</v>
       </c>
       <c r="D44">
-        <v>21.31080397191943</v>
+        <v>21.38498643429694</v>
       </c>
       <c r="E44">
-        <v>2.1606</v>
+        <v>2.3699</v>
       </c>
       <c r="F44">
-        <v>8.7906</v>
+        <v>8.9999</v>
       </c>
       <c r="G44">
         <v>1.46</v>
@@ -5252,28 +5252,28 @@
         <v>3.11</v>
       </c>
       <c r="M44">
-        <v>0.47732958</v>
+        <v>0.48869457</v>
       </c>
       <c r="N44">
-        <v>2.63267042</v>
+        <v>2.62130543</v>
       </c>
       <c r="O44">
-        <v>0.6318409007999999</v>
+        <v>0.6291133032</v>
       </c>
       <c r="P44">
-        <v>2.0008295192</v>
+        <v>1.9921921268</v>
       </c>
       <c r="Q44">
-        <v>3.3408295192</v>
+        <v>3.3321921268</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1577216190471222</v>
+        <v>0.1593811922832895</v>
       </c>
       <c r="T44">
-        <v>1.887159286150906</v>
+        <v>1.915142075091459</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.515414360031909</v>
+        <v>6.363893095845121</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5298,22 +5298,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.108592519601475</v>
+        <v>0.1083739401556192</v>
       </c>
       <c r="C45">
-        <v>13.84508643429694</v>
+        <v>13.71048715592033</v>
       </c>
       <c r="D45">
-        <v>21.38498643429694</v>
+        <v>21.45968715592033</v>
       </c>
       <c r="E45">
-        <v>2.3699</v>
+        <v>2.579199999999999</v>
       </c>
       <c r="F45">
-        <v>8.9999</v>
+        <v>9.209199999999999</v>
       </c>
       <c r="G45">
         <v>1.46</v>
@@ -5334,28 +5334,28 @@
         <v>3.11</v>
       </c>
       <c r="M45">
-        <v>0.48869457</v>
+        <v>0.50005956</v>
       </c>
       <c r="N45">
-        <v>2.62130543</v>
+        <v>2.60994044</v>
       </c>
       <c r="O45">
-        <v>0.6291133032</v>
+        <v>0.6263857056</v>
       </c>
       <c r="P45">
-        <v>1.9921921268</v>
+        <v>1.9835547344</v>
       </c>
       <c r="Q45">
-        <v>3.3321921268</v>
+        <v>3.3235547344</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1593811922832895</v>
+        <v>0.161100035992177</v>
       </c>
       <c r="T45">
-        <v>1.915142075091459</v>
+        <v>1.944124249351317</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.363893095845121</v>
+        <v>6.219259161848641</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5380,22 +5380,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1083739401556192</v>
+        <v>0.1084973607097633</v>
       </c>
       <c r="C46">
-        <v>13.71048715592033</v>
+        <v>13.45894348807593</v>
       </c>
       <c r="D46">
-        <v>21.45968715592033</v>
+        <v>21.41744348807593</v>
       </c>
       <c r="E46">
-        <v>2.579199999999999</v>
+        <v>2.7885</v>
       </c>
       <c r="F46">
-        <v>9.209199999999999</v>
+        <v>9.4185</v>
       </c>
       <c r="G46">
         <v>1.46</v>
@@ -5416,45 +5416,45 @@
         <v>3.11</v>
       </c>
       <c r="M46">
-        <v>0.50005956</v>
+        <v>0.52084305</v>
       </c>
       <c r="N46">
-        <v>2.60994044</v>
+        <v>2.58915695</v>
       </c>
       <c r="O46">
-        <v>0.6263857056</v>
+        <v>0.621397668</v>
       </c>
       <c r="P46">
-        <v>1.9835547344</v>
+        <v>1.967759282</v>
       </c>
       <c r="Q46">
-        <v>3.3235547344</v>
+        <v>3.307759282</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.161100035992177</v>
+        <v>0.1628813831086605</v>
       </c>
       <c r="T46">
-        <v>1.944124249351317</v>
+        <v>1.974160320856989</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.219259161848641</v>
+        <v>5.971088603371016</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5462,22 +5462,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1084973607097633</v>
+        <v>0.1082863812639074</v>
       </c>
       <c r="C47">
-        <v>13.45894348807593</v>
+        <v>13.3219574910213</v>
       </c>
       <c r="D47">
-        <v>21.41744348807593</v>
+        <v>21.4897574910213</v>
       </c>
       <c r="E47">
-        <v>2.7885</v>
+        <v>2.997800000000001</v>
       </c>
       <c r="F47">
-        <v>9.4185</v>
+        <v>9.627800000000001</v>
       </c>
       <c r="G47">
         <v>1.46</v>
@@ -5498,28 +5498,28 @@
         <v>3.11</v>
       </c>
       <c r="M47">
-        <v>0.52084305</v>
+        <v>0.5324173400000001</v>
       </c>
       <c r="N47">
-        <v>2.58915695</v>
+        <v>2.57758266</v>
       </c>
       <c r="O47">
-        <v>0.621397668</v>
+        <v>0.6186198384</v>
       </c>
       <c r="P47">
-        <v>1.967759282</v>
+        <v>1.9589628216</v>
       </c>
       <c r="Q47">
-        <v>3.307759282</v>
+        <v>3.2989628216</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1628813831086605</v>
+        <v>0.164728706044273</v>
       </c>
       <c r="T47">
-        <v>1.974160320856989</v>
+        <v>2.005308839455464</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.971088603371016</v>
+        <v>5.841282329384688</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5544,22 +5544,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1082863812639074</v>
+        <v>0.1080754018180516</v>
       </c>
       <c r="C48">
-        <v>13.3219574910213</v>
+        <v>13.18546147131964</v>
       </c>
       <c r="D48">
-        <v>21.4897574910213</v>
+        <v>21.56256147131964</v>
       </c>
       <c r="E48">
-        <v>2.997800000000001</v>
+        <v>3.207100000000001</v>
       </c>
       <c r="F48">
-        <v>9.627800000000001</v>
+        <v>9.837100000000001</v>
       </c>
       <c r="G48">
         <v>1.46</v>
@@ -5580,28 +5580,28 @@
         <v>3.11</v>
       </c>
       <c r="M48">
-        <v>0.5324173400000001</v>
+        <v>0.5439916300000001</v>
       </c>
       <c r="N48">
-        <v>2.57758266</v>
+        <v>2.56600837</v>
       </c>
       <c r="O48">
-        <v>0.6186198384</v>
+        <v>0.6158420087999998</v>
       </c>
       <c r="P48">
-        <v>1.9589628216</v>
+        <v>1.9501663612</v>
       </c>
       <c r="Q48">
-        <v>3.2989628216</v>
+        <v>3.2901663612</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.164728706044273</v>
+        <v>0.1666457392793425</v>
       </c>
       <c r="T48">
-        <v>2.005308839455464</v>
+        <v>2.037632773850107</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.841282329384688</v>
+        <v>5.716999726631822</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5626,22 +5626,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1080754018180516</v>
+        <v>0.1078644223721957</v>
       </c>
       <c r="C49">
-        <v>13.18546147131964</v>
+        <v>13.04946042580231</v>
       </c>
       <c r="D49">
-        <v>21.56256147131964</v>
+        <v>21.63586042580231</v>
       </c>
       <c r="E49">
-        <v>3.207100000000001</v>
+        <v>3.4164</v>
       </c>
       <c r="F49">
-        <v>9.837100000000001</v>
+        <v>10.0464</v>
       </c>
       <c r="G49">
         <v>1.46</v>
@@ -5662,28 +5662,28 @@
         <v>3.11</v>
       </c>
       <c r="M49">
-        <v>0.5439916300000001</v>
+        <v>0.55556592</v>
       </c>
       <c r="N49">
-        <v>2.56600837</v>
+        <v>2.55443408</v>
       </c>
       <c r="O49">
-        <v>0.6158420087999998</v>
+        <v>0.6130641792</v>
       </c>
       <c r="P49">
-        <v>1.9501663612</v>
+        <v>1.9413699008</v>
       </c>
       <c r="Q49">
-        <v>3.2901663612</v>
+        <v>3.281369900800001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1666457392793425</v>
+        <v>0.1686365045619148</v>
       </c>
       <c r="T49">
-        <v>2.037632773850107</v>
+        <v>2.071199936490697</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.716999726631822</v>
+        <v>5.597895565660327</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5708,22 +5708,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1078644223721957</v>
+        <v>0.1076534429263398</v>
       </c>
       <c r="C50">
-        <v>13.04946042580231</v>
+        <v>12.91395941947654</v>
       </c>
       <c r="D50">
-        <v>21.63586042580231</v>
+        <v>21.70965941947654</v>
       </c>
       <c r="E50">
-        <v>3.4164</v>
+        <v>3.625699999999999</v>
       </c>
       <c r="F50">
-        <v>10.0464</v>
+        <v>10.2557</v>
       </c>
       <c r="G50">
         <v>1.46</v>
@@ -5744,28 +5744,28 @@
         <v>3.11</v>
       </c>
       <c r="M50">
-        <v>0.55556592</v>
+        <v>0.5671402099999999</v>
       </c>
       <c r="N50">
-        <v>2.55443408</v>
+        <v>2.54285979</v>
       </c>
       <c r="O50">
-        <v>0.6130641792</v>
+        <v>0.6102863495999999</v>
       </c>
       <c r="P50">
-        <v>1.9413699008</v>
+        <v>1.9325734404</v>
       </c>
       <c r="Q50">
-        <v>3.281369900800001</v>
+        <v>3.2725734404</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1686365045619148</v>
+        <v>0.1707053390712545</v>
       </c>
       <c r="T50">
-        <v>2.071199936490697</v>
+        <v>2.106083458450527</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.597895565660327</v>
+        <v>5.483652799014199</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5790,22 +5790,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1076534429263398</v>
+        <v>0.107442463480484</v>
       </c>
       <c r="C51">
-        <v>12.91395941947654</v>
+        <v>12.77896358669222</v>
       </c>
       <c r="D51">
-        <v>21.70965941947654</v>
+        <v>21.78396358669222</v>
       </c>
       <c r="E51">
-        <v>3.625699999999999</v>
+        <v>3.835</v>
       </c>
       <c r="F51">
-        <v>10.2557</v>
+        <v>10.465</v>
       </c>
       <c r="G51">
         <v>1.46</v>
@@ -5826,28 +5826,28 @@
         <v>3.11</v>
       </c>
       <c r="M51">
-        <v>0.5671402099999999</v>
+        <v>0.5787145</v>
       </c>
       <c r="N51">
-        <v>2.54285979</v>
+        <v>2.5312855</v>
       </c>
       <c r="O51">
-        <v>0.6102863495999999</v>
+        <v>0.60750852</v>
       </c>
       <c r="P51">
-        <v>1.9325734404</v>
+        <v>1.92377698</v>
       </c>
       <c r="Q51">
-        <v>3.2725734404</v>
+        <v>3.26377698</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1707053390712545</v>
+        <v>0.1728569269609679</v>
       </c>
       <c r="T51">
-        <v>2.106083458450527</v>
+        <v>2.142362321288751</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.483652799014199</v>
+        <v>5.373979743033914</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5872,22 +5872,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.107442463480484</v>
+        <v>0.1072314840346281</v>
       </c>
       <c r="C52">
-        <v>12.77896358669222</v>
+        <v>12.6444781323326</v>
       </c>
       <c r="D52">
-        <v>21.78396358669222</v>
+        <v>21.8587781323326</v>
       </c>
       <c r="E52">
-        <v>3.835</v>
+        <v>4.044300000000001</v>
       </c>
       <c r="F52">
-        <v>10.465</v>
+        <v>10.6743</v>
       </c>
       <c r="G52">
         <v>1.46</v>
@@ -5908,28 +5908,28 @@
         <v>3.11</v>
       </c>
       <c r="M52">
-        <v>0.5787145</v>
+        <v>0.59028879</v>
       </c>
       <c r="N52">
-        <v>2.5312855</v>
+        <v>2.51971121</v>
       </c>
       <c r="O52">
-        <v>0.60750852</v>
+        <v>0.6047306903999999</v>
       </c>
       <c r="P52">
-        <v>1.92377698</v>
+        <v>1.9149805196</v>
       </c>
       <c r="Q52">
-        <v>3.26377698</v>
+        <v>3.2549805196</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1728569269609679</v>
+        <v>0.1750963347645471</v>
       </c>
       <c r="T52">
-        <v>2.142362321288751</v>
+        <v>2.180121954038738</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.373979743033914</v>
+        <v>5.268607591209719</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5954,22 +5954,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1072314840346281</v>
+        <v>0.1070205045887722</v>
       </c>
       <c r="C53">
-        <v>12.6444781323326</v>
+        <v>12.51050833302963</v>
       </c>
       <c r="D53">
-        <v>21.8587781323326</v>
+        <v>21.93410833302963</v>
       </c>
       <c r="E53">
-        <v>4.044300000000001</v>
+        <v>4.2536</v>
       </c>
       <c r="F53">
-        <v>10.6743</v>
+        <v>10.8836</v>
       </c>
       <c r="G53">
         <v>1.46</v>
@@ -5990,28 +5990,28 @@
         <v>3.11</v>
       </c>
       <c r="M53">
-        <v>0.59028879</v>
+        <v>0.60186308</v>
       </c>
       <c r="N53">
-        <v>2.51971121</v>
+        <v>2.50813692</v>
       </c>
       <c r="O53">
-        <v>0.6047306903999999</v>
+        <v>0.6019528608</v>
       </c>
       <c r="P53">
-        <v>1.9149805196</v>
+        <v>1.9061840592</v>
       </c>
       <c r="Q53">
-        <v>3.2549805196</v>
+        <v>3.2461840592</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1750963347645471</v>
+        <v>0.1774290512266088</v>
       </c>
       <c r="T53">
-        <v>2.180121954038738</v>
+        <v>2.219454904819975</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.268607591209719</v>
+        <v>5.167288214455687</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6036,22 +6036,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1070205045887722</v>
+        <v>0.1068095251429164</v>
       </c>
       <c r="C54">
-        <v>12.51050833302963</v>
+        <v>12.37705953840461</v>
       </c>
       <c r="D54">
-        <v>21.93410833302963</v>
+        <v>22.0099595384046</v>
       </c>
       <c r="E54">
-        <v>4.2536</v>
+        <v>4.4629</v>
       </c>
       <c r="F54">
-        <v>10.8836</v>
+        <v>11.0929</v>
       </c>
       <c r="G54">
         <v>1.46</v>
@@ -6072,28 +6072,28 @@
         <v>3.11</v>
       </c>
       <c r="M54">
-        <v>0.60186308</v>
+        <v>0.61343737</v>
       </c>
       <c r="N54">
-        <v>2.50813692</v>
+        <v>2.49656263</v>
       </c>
       <c r="O54">
-        <v>0.6019528608</v>
+        <v>0.5991750311999999</v>
       </c>
       <c r="P54">
-        <v>1.9061840592</v>
+        <v>1.8973875988</v>
       </c>
       <c r="Q54">
-        <v>3.2461840592</v>
+        <v>3.2373875988</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1774290512266088</v>
+        <v>0.179861032218971</v>
       </c>
       <c r="T54">
-        <v>2.219454904819975</v>
+        <v>2.260461598187647</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.167288214455687</v>
+        <v>5.069792210409353</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6118,22 +6118,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1068095251429164</v>
+        <v>0.1065985456970605</v>
       </c>
       <c r="C55">
-        <v>12.37705953840461</v>
+        <v>12.24413717233455</v>
       </c>
       <c r="D55">
-        <v>22.0099595384046</v>
+        <v>22.08633717233455</v>
       </c>
       <c r="E55">
-        <v>4.4629</v>
+        <v>4.672200000000001</v>
       </c>
       <c r="F55">
-        <v>11.0929</v>
+        <v>11.3022</v>
       </c>
       <c r="G55">
         <v>1.46</v>
@@ -6154,28 +6154,28 @@
         <v>3.11</v>
       </c>
       <c r="M55">
-        <v>0.61343737</v>
+        <v>0.6250116600000001</v>
       </c>
       <c r="N55">
-        <v>2.49656263</v>
+        <v>2.48498834</v>
       </c>
       <c r="O55">
-        <v>0.5991750311999999</v>
+        <v>0.5963972015999999</v>
       </c>
       <c r="P55">
-        <v>1.8973875988</v>
+        <v>1.8885911384</v>
       </c>
       <c r="Q55">
-        <v>3.2373875988</v>
+        <v>3.2285911384</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.179861032218971</v>
+        <v>0.1823987515153489</v>
       </c>
       <c r="T55">
-        <v>2.260461598187647</v>
+        <v>2.303251191266957</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.069792210409353</v>
+        <v>4.975907169475845</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6200,22 +6200,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1065985456970605</v>
+        <v>0.1063875662512046</v>
       </c>
       <c r="C56">
-        <v>12.24413717233455</v>
+        <v>12.11174673424507</v>
       </c>
       <c r="D56">
-        <v>22.08633717233455</v>
+        <v>22.16324673424507</v>
       </c>
       <c r="E56">
-        <v>4.672200000000001</v>
+        <v>4.881500000000002</v>
       </c>
       <c r="F56">
-        <v>11.3022</v>
+        <v>11.5115</v>
       </c>
       <c r="G56">
         <v>1.46</v>
@@ -6236,28 +6236,28 @@
         <v>3.11</v>
       </c>
       <c r="M56">
-        <v>0.6250116600000001</v>
+        <v>0.6365859500000001</v>
       </c>
       <c r="N56">
-        <v>2.48498834</v>
+        <v>2.47341405</v>
       </c>
       <c r="O56">
-        <v>0.5963972015999999</v>
+        <v>0.5936193719999999</v>
       </c>
       <c r="P56">
-        <v>1.8885911384</v>
+        <v>1.879794678</v>
       </c>
       <c r="Q56">
-        <v>3.2285911384</v>
+        <v>3.219794678</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1823987515153489</v>
+        <v>0.1850492583360103</v>
       </c>
       <c r="T56">
-        <v>2.303251191266957</v>
+        <v>2.347942544038681</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.975907169475845</v>
+        <v>4.88543613003083</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6282,22 +6282,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1063875662512046</v>
+        <v>0.1061765868053488</v>
       </c>
       <c r="C57">
-        <v>12.11174673424507</v>
+        <v>11.97989380043039</v>
       </c>
       <c r="D57">
-        <v>22.16324673424507</v>
+        <v>22.24069380043039</v>
       </c>
       <c r="E57">
-        <v>4.881500000000002</v>
+        <v>5.090800000000001</v>
       </c>
       <c r="F57">
-        <v>11.5115</v>
+        <v>11.7208</v>
       </c>
       <c r="G57">
         <v>1.46</v>
@@ -6318,28 +6318,28 @@
         <v>3.11</v>
       </c>
       <c r="M57">
-        <v>0.6365859500000001</v>
+        <v>0.6481602400000001</v>
       </c>
       <c r="N57">
-        <v>2.47341405</v>
+        <v>2.46183976</v>
       </c>
       <c r="O57">
-        <v>0.5936193719999999</v>
+        <v>0.5908415423999999</v>
       </c>
       <c r="P57">
-        <v>1.879794678</v>
+        <v>1.8709982176</v>
       </c>
       <c r="Q57">
-        <v>3.219794678</v>
+        <v>3.2109982176</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1850492583360103</v>
+        <v>0.187820242739429</v>
       </c>
       <c r="T57">
-        <v>2.347942544038681</v>
+        <v>2.394665321936392</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.88543613003083</v>
+        <v>4.798196199137422</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6364,22 +6364,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1061765868053488</v>
+        <v>0.1059656073594929</v>
       </c>
       <c r="C58">
-        <v>11.97989380043039</v>
+        <v>11.84858402540108</v>
       </c>
       <c r="D58">
-        <v>22.24069380043039</v>
+        <v>22.31868402540108</v>
       </c>
       <c r="E58">
-        <v>5.090800000000001</v>
+        <v>5.300100000000001</v>
       </c>
       <c r="F58">
-        <v>11.7208</v>
+        <v>11.9301</v>
       </c>
       <c r="G58">
         <v>1.46</v>
@@ -6400,28 +6400,28 @@
         <v>3.11</v>
       </c>
       <c r="M58">
-        <v>0.6481602400000001</v>
+        <v>0.65973453</v>
       </c>
       <c r="N58">
-        <v>2.46183976</v>
+        <v>2.45026547</v>
       </c>
       <c r="O58">
-        <v>0.5908415423999999</v>
+        <v>0.5880637127999999</v>
       </c>
       <c r="P58">
-        <v>1.8709982176</v>
+        <v>1.8622017572</v>
       </c>
       <c r="Q58">
-        <v>3.2109982176</v>
+        <v>3.2022017572</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.187820242739429</v>
+        <v>0.1907201101383556</v>
       </c>
       <c r="T58">
-        <v>2.394665321936392</v>
+        <v>2.443561252294463</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.798196199137422</v>
+        <v>4.714017318450801</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6446,22 +6446,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1059656073594929</v>
+        <v>0.105754627913637</v>
       </c>
       <c r="C59">
-        <v>11.84858402540108</v>
+        <v>11.71782314326024</v>
       </c>
       <c r="D59">
-        <v>22.31868402540108</v>
+        <v>22.39722314326024</v>
       </c>
       <c r="E59">
-        <v>5.300100000000001</v>
+        <v>5.509400000000002</v>
       </c>
       <c r="F59">
-        <v>11.9301</v>
+        <v>12.1394</v>
       </c>
       <c r="G59">
         <v>1.46</v>
@@ -6482,28 +6482,28 @@
         <v>3.11</v>
       </c>
       <c r="M59">
-        <v>0.65973453</v>
+        <v>0.6713088200000001</v>
       </c>
       <c r="N59">
-        <v>2.45026547</v>
+        <v>2.43869118</v>
       </c>
       <c r="O59">
-        <v>0.5880637127999999</v>
+        <v>0.5852858832</v>
       </c>
       <c r="P59">
-        <v>1.8622017572</v>
+        <v>1.8534052968</v>
       </c>
       <c r="Q59">
-        <v>3.2022017572</v>
+        <v>3.1934052968</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1907201101383556</v>
+        <v>0.1937580664610406</v>
       </c>
       <c r="T59">
-        <v>2.443561252294463</v>
+        <v>2.494785560288632</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.714017318450801</v>
+        <v>4.632741157787856</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6528,22 +6528,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.105754627913637</v>
+        <v>0.1055436484677812</v>
       </c>
       <c r="C60">
-        <v>11.71782314326024</v>
+        <v>11.58761696910891</v>
       </c>
       <c r="D60">
-        <v>22.39722314326023</v>
+        <v>22.47631696910891</v>
       </c>
       <c r="E60">
-        <v>5.509399999999999</v>
+        <v>5.718699999999999</v>
       </c>
       <c r="F60">
-        <v>12.1394</v>
+        <v>12.3487</v>
       </c>
       <c r="G60">
         <v>1.46</v>
@@ -6564,28 +6564,28 @@
         <v>3.11</v>
       </c>
       <c r="M60">
-        <v>0.6713088199999999</v>
+        <v>0.68288311</v>
       </c>
       <c r="N60">
-        <v>2.43869118</v>
+        <v>2.42711689</v>
       </c>
       <c r="O60">
-        <v>0.5852858832</v>
+        <v>0.5825080535999999</v>
       </c>
       <c r="P60">
-        <v>1.8534052968</v>
+        <v>1.8446088364</v>
       </c>
       <c r="Q60">
-        <v>3.1934052968</v>
+        <v>3.1846088364</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1937580664610406</v>
+        <v>0.196944215775076</v>
       </c>
       <c r="T60">
-        <v>2.494785560288632</v>
+        <v>2.548508615014223</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.632741157787858</v>
+        <v>4.554220121215181</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6610,22 +6610,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1055436484677812</v>
+        <v>0.1064726690219253</v>
       </c>
       <c r="C61">
-        <v>11.58761696910891</v>
+        <v>11.03415936433608</v>
       </c>
       <c r="D61">
-        <v>22.47631696910891</v>
+        <v>22.13215936433608</v>
       </c>
       <c r="E61">
-        <v>5.718699999999999</v>
+        <v>5.928</v>
       </c>
       <c r="F61">
-        <v>12.3487</v>
+        <v>12.558</v>
       </c>
       <c r="G61">
         <v>1.46</v>
@@ -6646,45 +6646,45 @@
         <v>3.11</v>
       </c>
       <c r="M61">
-        <v>0.68288311</v>
+        <v>0.7258524000000001</v>
       </c>
       <c r="N61">
-        <v>2.42711689</v>
+        <v>2.3841476</v>
       </c>
       <c r="O61">
-        <v>0.5825080535999999</v>
+        <v>0.572195424</v>
       </c>
       <c r="P61">
-        <v>1.8446088364</v>
+        <v>1.811952176</v>
       </c>
       <c r="Q61">
-        <v>3.1846088364</v>
+        <v>3.151952176</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.196944215775076</v>
+        <v>0.2002896725548132</v>
       </c>
       <c r="T61">
-        <v>2.548508615014223</v>
+        <v>2.604917822476094</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.24</v>
       </c>
       <c r="W61">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.554220121215181</v>
+        <v>4.284617644027904</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6692,22 +6692,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1064726690219253</v>
+        <v>0.1062806895760694</v>
       </c>
       <c r="C62">
-        <v>11.03415936433608</v>
+        <v>10.89511186509527</v>
       </c>
       <c r="D62">
-        <v>22.13215936433608</v>
+        <v>22.20241186509526</v>
       </c>
       <c r="E62">
-        <v>5.928</v>
+        <v>6.137299999999999</v>
       </c>
       <c r="F62">
-        <v>12.558</v>
+        <v>12.7673</v>
       </c>
       <c r="G62">
         <v>1.46</v>
@@ -6728,28 +6728,28 @@
         <v>3.11</v>
       </c>
       <c r="M62">
-        <v>0.7258524000000001</v>
+        <v>0.73794994</v>
       </c>
       <c r="N62">
-        <v>2.3841476</v>
+        <v>2.37205006</v>
       </c>
       <c r="O62">
-        <v>0.572195424</v>
+        <v>0.5692920144</v>
       </c>
       <c r="P62">
-        <v>1.811952176</v>
+        <v>1.8027580456</v>
       </c>
       <c r="Q62">
-        <v>3.151952176</v>
+        <v>3.1427580456</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2002896725548132</v>
+        <v>0.2038066912206909</v>
       </c>
       <c r="T62">
-        <v>2.604917822476094</v>
+        <v>2.664219809807805</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.284617644027904</v>
+        <v>4.214378010519249</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6774,22 +6774,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1062806895760694</v>
+        <v>0.1060887101302136</v>
       </c>
       <c r="C63">
-        <v>10.89511186509527</v>
+        <v>10.75651178083933</v>
       </c>
       <c r="D63">
-        <v>22.20241186509526</v>
+        <v>22.27311178083933</v>
       </c>
       <c r="E63">
-        <v>6.137299999999999</v>
+        <v>6.3466</v>
       </c>
       <c r="F63">
-        <v>12.7673</v>
+        <v>12.9766</v>
       </c>
       <c r="G63">
         <v>1.46</v>
@@ -6810,28 +6810,28 @@
         <v>3.11</v>
       </c>
       <c r="M63">
-        <v>0.73794994</v>
+        <v>0.75004748</v>
       </c>
       <c r="N63">
-        <v>2.37205006</v>
+        <v>2.35995252</v>
       </c>
       <c r="O63">
-        <v>0.5692920144</v>
+        <v>0.5663886048</v>
       </c>
       <c r="P63">
-        <v>1.8027580456</v>
+        <v>1.7935639152</v>
       </c>
       <c r="Q63">
-        <v>3.1427580456</v>
+        <v>3.1335639152</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2038066912206909</v>
+        <v>0.207508816132141</v>
       </c>
       <c r="T63">
-        <v>2.664219809807805</v>
+        <v>2.726642954367501</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.214378010519249</v>
+        <v>4.146404171639907</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6856,22 +6856,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1060887101302136</v>
+        <v>0.1058967306843577</v>
       </c>
       <c r="C64">
-        <v>10.75651178083933</v>
+        <v>10.61836339937961</v>
       </c>
       <c r="D64">
-        <v>22.27311178083933</v>
+        <v>22.34426339937961</v>
       </c>
       <c r="E64">
-        <v>6.3466</v>
+        <v>6.5559</v>
       </c>
       <c r="F64">
-        <v>12.9766</v>
+        <v>13.1859</v>
       </c>
       <c r="G64">
         <v>1.46</v>
@@ -6892,28 +6892,28 @@
         <v>3.11</v>
       </c>
       <c r="M64">
-        <v>0.75004748</v>
+        <v>0.7621450200000001</v>
       </c>
       <c r="N64">
-        <v>2.35995252</v>
+        <v>2.34785498</v>
       </c>
       <c r="O64">
-        <v>0.5663886048</v>
+        <v>0.5634851952</v>
       </c>
       <c r="P64">
-        <v>1.7935639152</v>
+        <v>1.7843697848</v>
       </c>
       <c r="Q64">
-        <v>3.1335639152</v>
+        <v>3.1243697848</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.207508816132141</v>
+        <v>0.2114110559036695</v>
       </c>
       <c r="T64">
-        <v>2.726642954367501</v>
+        <v>2.79244032295745</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.146404171639907</v>
+        <v>4.080588232407527</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6938,22 +6938,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1058967306843577</v>
+        <v>0.1057047512385018</v>
       </c>
       <c r="C65">
-        <v>10.61836339937961</v>
+        <v>10.48067106349279</v>
       </c>
       <c r="D65">
-        <v>22.34426339937961</v>
+        <v>22.41587106349279</v>
       </c>
       <c r="E65">
-        <v>6.5559</v>
+        <v>6.765200000000001</v>
       </c>
       <c r="F65">
-        <v>13.1859</v>
+        <v>13.3952</v>
       </c>
       <c r="G65">
         <v>1.46</v>
@@ -6974,28 +6974,28 @@
         <v>3.11</v>
       </c>
       <c r="M65">
-        <v>0.7621450200000001</v>
+        <v>0.7742425600000001</v>
       </c>
       <c r="N65">
-        <v>2.34785498</v>
+        <v>2.33575744</v>
       </c>
       <c r="O65">
-        <v>0.5634851952</v>
+        <v>0.5605817855999999</v>
       </c>
       <c r="P65">
-        <v>1.7843697848</v>
+        <v>1.7751756544</v>
       </c>
       <c r="Q65">
-        <v>3.1243697848</v>
+        <v>3.1151756544</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2114110559036695</v>
+        <v>0.2155300867736162</v>
       </c>
       <c r="T65">
-        <v>2.79244032295745</v>
+        <v>2.861893100913508</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.080588232407527</v>
+        <v>4.016829041276159</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7020,22 +7020,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1057047512385018</v>
+        <v>0.107241771792646</v>
       </c>
       <c r="C66">
-        <v>10.48067106349279</v>
+        <v>9.71061811711118</v>
       </c>
       <c r="D66">
-        <v>22.41587106349279</v>
+        <v>21.85511811711118</v>
       </c>
       <c r="E66">
-        <v>6.765200000000001</v>
+        <v>6.9745</v>
       </c>
       <c r="F66">
-        <v>13.3952</v>
+        <v>13.6045</v>
       </c>
       <c r="G66">
         <v>1.46</v>
@@ -7056,45 +7056,45 @@
         <v>3.11</v>
       </c>
       <c r="M66">
-        <v>0.7742425600000001</v>
+        <v>0.8339558499999999</v>
       </c>
       <c r="N66">
-        <v>2.33575744</v>
+        <v>2.27604415</v>
       </c>
       <c r="O66">
-        <v>0.5605817855999999</v>
+        <v>0.5462505959999999</v>
       </c>
       <c r="P66">
-        <v>1.7751756544</v>
+        <v>1.729793554</v>
       </c>
       <c r="Q66">
-        <v>3.1151756544</v>
+        <v>3.069793554</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2155300867736162</v>
+        <v>0.2198844908361314</v>
       </c>
       <c r="T66">
-        <v>2.861893100913508</v>
+        <v>2.935314609038484</v>
       </c>
       <c r="U66">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.016829041276159</v>
+        <v>3.729214202406518</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7102,22 +7102,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.107241771792646</v>
+        <v>0.1070763923467901</v>
       </c>
       <c r="C67">
-        <v>9.71061811711118</v>
+        <v>9.560303106026112</v>
       </c>
       <c r="D67">
-        <v>21.85511811711118</v>
+        <v>21.91410310602611</v>
       </c>
       <c r="E67">
-        <v>6.9745</v>
+        <v>7.183800000000001</v>
       </c>
       <c r="F67">
-        <v>13.6045</v>
+        <v>13.8138</v>
       </c>
       <c r="G67">
         <v>1.46</v>
@@ -7138,28 +7138,28 @@
         <v>3.11</v>
       </c>
       <c r="M67">
-        <v>0.8339558499999999</v>
+        <v>0.8467859400000001</v>
       </c>
       <c r="N67">
-        <v>2.27604415</v>
+        <v>2.26321406</v>
       </c>
       <c r="O67">
-        <v>0.5462505959999999</v>
+        <v>0.5431713743999999</v>
       </c>
       <c r="P67">
-        <v>1.729793554</v>
+        <v>1.7200426856</v>
       </c>
       <c r="Q67">
-        <v>3.069793554</v>
+        <v>3.0600426856</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2198844908361314</v>
+        <v>0.2244950363140886</v>
       </c>
       <c r="T67">
-        <v>2.935314609038484</v>
+        <v>3.013055029406104</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.729214202406518</v>
+        <v>3.67271095691551</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7184,22 +7184,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1070763923467901</v>
+        <v>0.1069110129009342</v>
       </c>
       <c r="C68">
-        <v>9.560303106026112</v>
+        <v>9.410307346883281</v>
       </c>
       <c r="D68">
-        <v>21.91410310602611</v>
+        <v>21.97340734688328</v>
       </c>
       <c r="E68">
-        <v>7.183800000000001</v>
+        <v>7.393100000000001</v>
       </c>
       <c r="F68">
-        <v>13.8138</v>
+        <v>14.0231</v>
       </c>
       <c r="G68">
         <v>1.46</v>
@@ -7220,28 +7220,28 @@
         <v>3.11</v>
       </c>
       <c r="M68">
-        <v>0.8467859400000001</v>
+        <v>0.8596160300000001</v>
       </c>
       <c r="N68">
-        <v>2.26321406</v>
+        <v>2.25038397</v>
       </c>
       <c r="O68">
-        <v>0.5431713743999999</v>
+        <v>0.5400921527999999</v>
       </c>
       <c r="P68">
-        <v>1.7200426856</v>
+        <v>1.7102918172</v>
       </c>
       <c r="Q68">
-        <v>3.0600426856</v>
+        <v>3.0502918172</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2244950363140886</v>
+        <v>0.2293850087907099</v>
       </c>
       <c r="T68">
-        <v>3.013055029406104</v>
+        <v>3.095506990402066</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.67271095691551</v>
+        <v>3.61789437546901</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7266,22 +7266,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1069110129009342</v>
+        <v>0.1067456334550784</v>
       </c>
       <c r="C69">
-        <v>9.410307346883281</v>
+        <v>9.260633438607664</v>
       </c>
       <c r="D69">
-        <v>21.97340734688328</v>
+        <v>22.03303343860766</v>
       </c>
       <c r="E69">
-        <v>7.393100000000001</v>
+        <v>7.6024</v>
       </c>
       <c r="F69">
-        <v>14.0231</v>
+        <v>14.2324</v>
       </c>
       <c r="G69">
         <v>1.46</v>
@@ -7302,28 +7302,28 @@
         <v>3.11</v>
       </c>
       <c r="M69">
-        <v>0.8596160300000001</v>
+        <v>0.87244612</v>
       </c>
       <c r="N69">
-        <v>2.25038397</v>
+        <v>2.23755388</v>
       </c>
       <c r="O69">
-        <v>0.5400921527999999</v>
+        <v>0.5370129312</v>
       </c>
       <c r="P69">
-        <v>1.7102918172</v>
+        <v>1.7005409488</v>
       </c>
       <c r="Q69">
-        <v>3.0502918172</v>
+        <v>3.0405409488</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2293850087907099</v>
+        <v>0.23458060454712</v>
       </c>
       <c r="T69">
-        <v>3.095506990402066</v>
+        <v>3.183112198960274</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.61789437546901</v>
+        <v>3.564690046417995</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7348,22 +7348,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1067456334550784</v>
+        <v>0.1065802540092225</v>
       </c>
       <c r="C70">
-        <v>9.260633438607664</v>
+        <v>9.111284008410269</v>
       </c>
       <c r="D70">
-        <v>22.03303343860766</v>
+        <v>22.09298400841027</v>
       </c>
       <c r="E70">
-        <v>7.6024</v>
+        <v>7.811700000000001</v>
       </c>
       <c r="F70">
-        <v>14.2324</v>
+        <v>14.4417</v>
       </c>
       <c r="G70">
         <v>1.46</v>
@@ -7384,28 +7384,28 @@
         <v>3.11</v>
       </c>
       <c r="M70">
-        <v>0.87244612</v>
+        <v>0.88527621</v>
       </c>
       <c r="N70">
-        <v>2.23755388</v>
+        <v>2.22472379</v>
       </c>
       <c r="O70">
-        <v>0.5370129312</v>
+        <v>0.5339337095999999</v>
       </c>
       <c r="P70">
-        <v>1.7005409488</v>
+        <v>1.6907900804</v>
       </c>
       <c r="Q70">
-        <v>3.0405409488</v>
+        <v>3.0307900804</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.23458060454712</v>
+        <v>0.2401114000297501</v>
       </c>
       <c r="T70">
-        <v>3.183112198960274</v>
+        <v>3.276369356457723</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.564690046417995</v>
+        <v>3.513027871832227</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7430,22 +7430,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1065802540092225</v>
+        <v>0.1079044745633667</v>
       </c>
       <c r="C71">
-        <v>9.111284008410269</v>
+        <v>8.430907105626657</v>
       </c>
       <c r="D71">
-        <v>22.09298400841027</v>
+        <v>21.62190710562666</v>
       </c>
       <c r="E71">
-        <v>7.811700000000001</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="F71">
-        <v>14.4417</v>
+        <v>14.651</v>
       </c>
       <c r="G71">
         <v>1.46</v>
@@ -7466,45 +7466,45 @@
         <v>3.11</v>
       </c>
       <c r="M71">
-        <v>0.88527621</v>
+        <v>0.9391291000000002</v>
       </c>
       <c r="N71">
-        <v>2.22472379</v>
+        <v>2.1708709</v>
       </c>
       <c r="O71">
-        <v>0.5339337095999999</v>
+        <v>0.5210090159999999</v>
       </c>
       <c r="P71">
-        <v>1.6907900804</v>
+        <v>1.649861884</v>
       </c>
       <c r="Q71">
-        <v>3.0307900804</v>
+        <v>2.989861884</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2401114000297501</v>
+        <v>0.2460109152112222</v>
       </c>
       <c r="T71">
-        <v>3.276369356457723</v>
+        <v>3.375843657788335</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.24</v>
       </c>
       <c r="W71">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.513027871832227</v>
+        <v>3.31157878080873</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7512,22 +7512,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1079044745633667</v>
+        <v>0.1077603751175108</v>
       </c>
       <c r="C72">
-        <v>8.430907105626657</v>
+        <v>8.271892547352257</v>
       </c>
       <c r="D72">
-        <v>21.62190710562666</v>
+        <v>21.67219254735226</v>
       </c>
       <c r="E72">
-        <v>8.021000000000001</v>
+        <v>8.2303</v>
       </c>
       <c r="F72">
-        <v>14.651</v>
+        <v>14.8603</v>
       </c>
       <c r="G72">
         <v>1.46</v>
@@ -7548,28 +7548,28 @@
         <v>3.11</v>
       </c>
       <c r="M72">
-        <v>0.9391291000000002</v>
+        <v>0.9525452300000001</v>
       </c>
       <c r="N72">
-        <v>2.1708709</v>
+        <v>2.15745477</v>
       </c>
       <c r="O72">
-        <v>0.5210090159999999</v>
+        <v>0.5177891447999999</v>
       </c>
       <c r="P72">
-        <v>1.649861884</v>
+        <v>1.6396656252</v>
       </c>
       <c r="Q72">
-        <v>2.989861884</v>
+        <v>2.9796656252</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2460109152112222</v>
+        <v>0.2523172935086579</v>
       </c>
       <c r="T72">
-        <v>3.375843657788335</v>
+        <v>3.482178255762437</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7586,7 +7586,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.31157878080873</v>
+        <v>3.264936826149452</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7594,22 +7594,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1077603751175108</v>
+        <v>0.1076162756716549</v>
       </c>
       <c r="C73">
-        <v>8.271892547352259</v>
+        <v>8.113112429092515</v>
       </c>
       <c r="D73">
-        <v>21.67219254735226</v>
+        <v>21.72271242909251</v>
       </c>
       <c r="E73">
-        <v>8.2303</v>
+        <v>8.439599999999999</v>
       </c>
       <c r="F73">
-        <v>14.8603</v>
+        <v>15.0696</v>
       </c>
       <c r="G73">
         <v>1.46</v>
@@ -7630,28 +7630,28 @@
         <v>3.11</v>
       </c>
       <c r="M73">
-        <v>0.95254523</v>
+        <v>0.96596136</v>
       </c>
       <c r="N73">
-        <v>2.15745477</v>
+        <v>2.14403864</v>
       </c>
       <c r="O73">
-        <v>0.5177891447999999</v>
+        <v>0.5145692735999999</v>
       </c>
       <c r="P73">
-        <v>1.6396656252</v>
+        <v>1.6294693664</v>
       </c>
       <c r="Q73">
-        <v>2.9796656252</v>
+        <v>2.9694693664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2523172935086579</v>
+        <v>0.2590741273987676</v>
       </c>
       <c r="T73">
-        <v>3.482178255762436</v>
+        <v>3.59610818216326</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.264936826149452</v>
+        <v>3.219590481341821</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7676,22 +7676,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1076162756716549</v>
+        <v>0.107472176225799</v>
       </c>
       <c r="C74">
-        <v>8.113112429092515</v>
+        <v>7.954568394182154</v>
       </c>
       <c r="D74">
-        <v>21.72271242909251</v>
+        <v>21.77346839418215</v>
       </c>
       <c r="E74">
-        <v>8.439599999999999</v>
+        <v>8.648900000000001</v>
       </c>
       <c r="F74">
-        <v>15.0696</v>
+        <v>15.2789</v>
       </c>
       <c r="G74">
         <v>1.46</v>
@@ -7712,28 +7712,28 @@
         <v>3.11</v>
       </c>
       <c r="M74">
-        <v>0.96596136</v>
+        <v>0.9793774900000001</v>
       </c>
       <c r="N74">
-        <v>2.14403864</v>
+        <v>2.13062251</v>
       </c>
       <c r="O74">
-        <v>0.5145692735999999</v>
+        <v>0.5113494023999999</v>
       </c>
       <c r="P74">
-        <v>1.6294693664</v>
+        <v>1.6192731076</v>
       </c>
       <c r="Q74">
-        <v>2.9694693664</v>
+        <v>2.9592731076</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2590741273987676</v>
+        <v>0.2663314675029594</v>
       </c>
       <c r="T74">
-        <v>3.59610818216326</v>
+        <v>3.718477362371551</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.219590481341821</v>
+        <v>3.175486502145357</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7758,22 +7758,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.107472176225799</v>
+        <v>0.1073280767799432</v>
       </c>
       <c r="C75">
-        <v>7.954568394182154</v>
+        <v>7.796262101350724</v>
       </c>
       <c r="D75">
-        <v>21.77346839418215</v>
+        <v>21.82446210135072</v>
       </c>
       <c r="E75">
-        <v>8.648900000000001</v>
+        <v>8.8582</v>
       </c>
       <c r="F75">
-        <v>15.2789</v>
+        <v>15.4882</v>
       </c>
       <c r="G75">
         <v>1.46</v>
@@ -7794,28 +7794,28 @@
         <v>3.11</v>
       </c>
       <c r="M75">
-        <v>0.9793774900000001</v>
+        <v>0.99279362</v>
       </c>
       <c r="N75">
-        <v>2.13062251</v>
+        <v>2.11720638</v>
       </c>
       <c r="O75">
-        <v>0.5113494023999999</v>
+        <v>0.5081295311999999</v>
       </c>
       <c r="P75">
-        <v>1.6192731076</v>
+        <v>1.6090768488</v>
       </c>
       <c r="Q75">
-        <v>2.9592731076</v>
+        <v>2.9490768488</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2663314675029594</v>
+        <v>0.274147064538243</v>
       </c>
       <c r="T75">
-        <v>3.718477362371551</v>
+        <v>3.85025955644202</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.175486502145357</v>
+        <v>3.132574522386636</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7840,22 +7840,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1073280767799432</v>
+        <v>0.1071839773340873</v>
       </c>
       <c r="C76">
-        <v>7.796262101350724</v>
+        <v>7.638195224903322</v>
       </c>
       <c r="D76">
-        <v>21.82446210135072</v>
+        <v>21.87569522490332</v>
       </c>
       <c r="E76">
-        <v>8.8582</v>
+        <v>9.067499999999999</v>
       </c>
       <c r="F76">
-        <v>15.4882</v>
+        <v>15.6975</v>
       </c>
       <c r="G76">
         <v>1.46</v>
@@ -7876,28 +7876,28 @@
         <v>3.11</v>
       </c>
       <c r="M76">
-        <v>0.99279362</v>
+        <v>1.00620975</v>
       </c>
       <c r="N76">
-        <v>2.11720638</v>
+        <v>2.10379025</v>
       </c>
       <c r="O76">
-        <v>0.5081295311999999</v>
+        <v>0.5049096599999999</v>
       </c>
       <c r="P76">
-        <v>1.6090768488</v>
+        <v>1.59888059</v>
       </c>
       <c r="Q76">
-        <v>2.9490768488</v>
+        <v>2.93888059</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.274147064538243</v>
+        <v>0.2825879093363493</v>
       </c>
       <c r="T76">
-        <v>3.85025955644202</v>
+        <v>3.992584326038126</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.132574522386636</v>
+        <v>3.090806862088148</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7922,22 +7922,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1071839773340873</v>
+        <v>0.1070398778882315</v>
       </c>
       <c r="C77">
-        <v>7.638195224903322</v>
+        <v>7.480369454903805</v>
       </c>
       <c r="D77">
-        <v>21.87569522490332</v>
+        <v>21.9271694549038</v>
       </c>
       <c r="E77">
-        <v>9.067499999999999</v>
+        <v>9.276800000000001</v>
       </c>
       <c r="F77">
-        <v>15.6975</v>
+        <v>15.9068</v>
       </c>
       <c r="G77">
         <v>1.46</v>
@@ -7958,28 +7958,28 @@
         <v>3.11</v>
       </c>
       <c r="M77">
-        <v>1.00620975</v>
+        <v>1.01962588</v>
       </c>
       <c r="N77">
-        <v>2.10379025</v>
+        <v>2.09037412</v>
       </c>
       <c r="O77">
-        <v>0.5049096599999999</v>
+        <v>0.5016897887999999</v>
       </c>
       <c r="P77">
-        <v>1.59888059</v>
+        <v>1.5886843312</v>
       </c>
       <c r="Q77">
-        <v>2.93888059</v>
+        <v>2.9286843312</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2825879093363493</v>
+        <v>0.2917321578676311</v>
       </c>
       <c r="T77">
-        <v>3.992584326038126</v>
+        <v>4.146769493100574</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.090806862088148</v>
+        <v>3.050138350744882</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8004,22 +8004,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1070398778882315</v>
+        <v>0.1068957784423756</v>
       </c>
       <c r="C78">
-        <v>7.480369454903805</v>
+        <v>7.322786497360667</v>
       </c>
       <c r="D78">
-        <v>21.9271694549038</v>
+        <v>21.97888649736067</v>
       </c>
       <c r="E78">
-        <v>9.276800000000001</v>
+        <v>9.4861</v>
       </c>
       <c r="F78">
-        <v>15.9068</v>
+        <v>16.1161</v>
       </c>
       <c r="G78">
         <v>1.46</v>
@@ -8040,28 +8040,28 @@
         <v>3.11</v>
       </c>
       <c r="M78">
-        <v>1.01962588</v>
+        <v>1.03304201</v>
       </c>
       <c r="N78">
-        <v>2.09037412</v>
+        <v>2.07695799</v>
       </c>
       <c r="O78">
-        <v>0.5016897887999999</v>
+        <v>0.4984699176</v>
       </c>
       <c r="P78">
-        <v>1.5886843312</v>
+        <v>1.5784880724</v>
       </c>
       <c r="Q78">
-        <v>2.9286843312</v>
+        <v>2.9184880724</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2917321578676311</v>
+        <v>0.3016715584451113</v>
       </c>
       <c r="T78">
-        <v>4.146769493100574</v>
+        <v>4.31436206599454</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.050138350744882</v>
+        <v>3.010526164371573</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8086,22 +8086,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1068957784423756</v>
+        <v>0.1113755189965197</v>
       </c>
       <c r="C79">
-        <v>7.322786497360667</v>
+        <v>5.612015968665599</v>
       </c>
       <c r="D79">
-        <v>21.97888649736067</v>
+        <v>20.4774159686656</v>
       </c>
       <c r="E79">
-        <v>9.4861</v>
+        <v>9.695400000000003</v>
       </c>
       <c r="F79">
-        <v>16.1161</v>
+        <v>16.3254</v>
       </c>
       <c r="G79">
         <v>1.46</v>
@@ -8122,45 +8122,45 @@
         <v>3.11</v>
       </c>
       <c r="M79">
-        <v>1.03304201</v>
+        <v>1.17379626</v>
       </c>
       <c r="N79">
-        <v>2.07695799</v>
+        <v>1.93620374</v>
       </c>
       <c r="O79">
-        <v>0.4984699176</v>
+        <v>0.4646888975999999</v>
       </c>
       <c r="P79">
-        <v>1.5784880724</v>
+        <v>1.4715148424</v>
       </c>
       <c r="Q79">
-        <v>2.9184880724</v>
+        <v>2.8115148424</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3016715584451113</v>
+        <v>0.3125145408932715</v>
       </c>
       <c r="T79">
-        <v>4.31436206599454</v>
+        <v>4.497190327333411</v>
       </c>
       <c r="U79">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.24</v>
       </c>
       <c r="W79">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.010526164371573</v>
+        <v>2.649522839679178</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8168,22 +8168,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1113755189965197</v>
+        <v>0.1112906995506639</v>
       </c>
       <c r="C80">
-        <v>5.612015968665599</v>
+        <v>5.429237033289112</v>
       </c>
       <c r="D80">
-        <v>20.4774159686656</v>
+        <v>20.50393703328911</v>
       </c>
       <c r="E80">
-        <v>9.695400000000003</v>
+        <v>9.904700000000002</v>
       </c>
       <c r="F80">
-        <v>16.3254</v>
+        <v>16.5347</v>
       </c>
       <c r="G80">
         <v>1.46</v>
@@ -8204,28 +8204,28 @@
         <v>3.11</v>
       </c>
       <c r="M80">
-        <v>1.17379626</v>
+        <v>1.18884493</v>
       </c>
       <c r="N80">
-        <v>1.93620374</v>
+        <v>1.92115507</v>
       </c>
       <c r="O80">
-        <v>0.4646888975999999</v>
+        <v>0.4610772167999999</v>
       </c>
       <c r="P80">
-        <v>1.4715148424</v>
+        <v>1.4600778532</v>
       </c>
       <c r="Q80">
-        <v>2.8115148424</v>
+        <v>2.8000778532</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3125145408932715</v>
+        <v>0.3243901883364946</v>
       </c>
       <c r="T80">
-        <v>4.497190327333411</v>
+        <v>4.697430804037888</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.649522839679178</v>
+        <v>2.615984575885771</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8250,22 +8250,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1112906995506639</v>
+        <v>0.111205880104808</v>
       </c>
       <c r="C81">
-        <v>5.429237033289112</v>
+        <v>5.246526883838335</v>
       </c>
       <c r="D81">
-        <v>20.50393703328911</v>
+        <v>20.53052688383833</v>
       </c>
       <c r="E81">
-        <v>9.904700000000002</v>
+        <v>10.114</v>
       </c>
       <c r="F81">
-        <v>16.5347</v>
+        <v>16.744</v>
       </c>
       <c r="G81">
         <v>1.46</v>
@@ -8286,28 +8286,28 @@
         <v>3.11</v>
       </c>
       <c r="M81">
-        <v>1.18884493</v>
+        <v>1.2038936</v>
       </c>
       <c r="N81">
-        <v>1.92115507</v>
+        <v>1.9061064</v>
       </c>
       <c r="O81">
-        <v>0.4610772167999999</v>
+        <v>0.457465536</v>
       </c>
       <c r="P81">
-        <v>1.4600778532</v>
+        <v>1.448640864</v>
       </c>
       <c r="Q81">
-        <v>2.8000778532</v>
+        <v>2.788640864</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3243901883364946</v>
+        <v>0.33745340052404</v>
       </c>
       <c r="T81">
-        <v>4.697430804037888</v>
+        <v>4.917695328412814</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.615984575885771</v>
+        <v>2.5832847686872</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8332,22 +8332,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.111205880104808</v>
+        <v>0.1111210606589521</v>
       </c>
       <c r="C82">
-        <v>5.246526883838335</v>
+        <v>5.06388578826899</v>
       </c>
       <c r="D82">
-        <v>20.53052688383833</v>
+        <v>20.55718578826899</v>
       </c>
       <c r="E82">
-        <v>10.114</v>
+        <v>10.3233</v>
       </c>
       <c r="F82">
-        <v>16.744</v>
+        <v>16.9533</v>
       </c>
       <c r="G82">
         <v>1.46</v>
@@ -8368,28 +8368,28 @@
         <v>3.11</v>
       </c>
       <c r="M82">
-        <v>1.2038936</v>
+        <v>1.21894227</v>
       </c>
       <c r="N82">
-        <v>1.9061064</v>
+        <v>1.89105773</v>
       </c>
       <c r="O82">
-        <v>0.457465536</v>
+        <v>0.4538538551999999</v>
       </c>
       <c r="P82">
-        <v>1.448640864</v>
+        <v>1.4372038748</v>
       </c>
       <c r="Q82">
-        <v>2.788640864</v>
+        <v>2.7772038748</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.33745340052404</v>
+        <v>0.3518916876786956</v>
       </c>
       <c r="T82">
-        <v>4.917695328412814</v>
+        <v>5.161145592195628</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.5832847686872</v>
+        <v>2.551392364135505</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8414,22 +8414,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1111210606589521</v>
+        <v>0.1110362412130963</v>
       </c>
       <c r="C83">
-        <v>5.06388578826899</v>
+        <v>4.881314015930382</v>
       </c>
       <c r="D83">
-        <v>20.55718578826899</v>
+        <v>20.58391401593038</v>
       </c>
       <c r="E83">
-        <v>10.3233</v>
+        <v>10.5326</v>
       </c>
       <c r="F83">
-        <v>16.9533</v>
+        <v>17.1626</v>
       </c>
       <c r="G83">
         <v>1.46</v>
@@ -8450,28 +8450,28 @@
         <v>3.11</v>
       </c>
       <c r="M83">
-        <v>1.21894227</v>
+        <v>1.23399094</v>
       </c>
       <c r="N83">
-        <v>1.89105773</v>
+        <v>1.87600906</v>
       </c>
       <c r="O83">
-        <v>0.4538538551999999</v>
+        <v>0.4502421743999999</v>
       </c>
       <c r="P83">
-        <v>1.4372038748</v>
+        <v>1.4257668856</v>
       </c>
       <c r="Q83">
-        <v>2.7772038748</v>
+        <v>2.7657668856</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3518916876786956</v>
+        <v>0.367934228961646</v>
       </c>
       <c r="T83">
-        <v>5.161145592195628</v>
+        <v>5.431645885287642</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.551392364135505</v>
+        <v>2.520277823109462</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8496,22 +8496,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1110362412130963</v>
+        <v>0.1134115417672404</v>
       </c>
       <c r="C84">
-        <v>4.881314015930382</v>
+        <v>3.948868513098724</v>
       </c>
       <c r="D84">
-        <v>20.58391401593038</v>
+        <v>19.86076851309872</v>
       </c>
       <c r="E84">
-        <v>10.5326</v>
+        <v>10.7419</v>
       </c>
       <c r="F84">
-        <v>17.1626</v>
+        <v>17.3719</v>
       </c>
       <c r="G84">
         <v>1.46</v>
@@ -8532,45 +8532,45 @@
         <v>3.11</v>
       </c>
       <c r="M84">
-        <v>1.23399094</v>
+        <v>1.31679002</v>
       </c>
       <c r="N84">
-        <v>1.87600906</v>
+        <v>1.79320998</v>
       </c>
       <c r="O84">
-        <v>0.4502421743999999</v>
+        <v>0.4303703951999999</v>
       </c>
       <c r="P84">
-        <v>1.4257668856</v>
+        <v>1.3628395848</v>
       </c>
       <c r="Q84">
-        <v>2.7657668856</v>
+        <v>2.7028395848</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.367934228961646</v>
+        <v>0.3858641280425907</v>
       </c>
       <c r="T84">
-        <v>5.431645885287642</v>
+        <v>5.733969742272834</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.24</v>
       </c>
       <c r="W84">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.520277823109462</v>
+        <v>2.361804048302249</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8578,22 +8578,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1134115417672404</v>
+        <v>0.1133563623213845</v>
       </c>
       <c r="C85">
-        <v>3.948868513098724</v>
+        <v>3.755790615106097</v>
       </c>
       <c r="D85">
-        <v>19.86076851309872</v>
+        <v>19.8769906151061</v>
       </c>
       <c r="E85">
-        <v>10.7419</v>
+        <v>10.9512</v>
       </c>
       <c r="F85">
-        <v>17.3719</v>
+        <v>17.5812</v>
       </c>
       <c r="G85">
         <v>1.46</v>
@@ -8614,28 +8614,28 @@
         <v>3.11</v>
       </c>
       <c r="M85">
-        <v>1.31679002</v>
+        <v>1.33265496</v>
       </c>
       <c r="N85">
-        <v>1.79320998</v>
+        <v>1.777345039999999</v>
       </c>
       <c r="O85">
-        <v>0.4303703951999999</v>
+        <v>0.4265628095999999</v>
       </c>
       <c r="P85">
-        <v>1.3628395848</v>
+        <v>1.3507822304</v>
       </c>
       <c r="Q85">
-        <v>2.7028395848</v>
+        <v>2.6907822304</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3858641280425907</v>
+        <v>0.4060352645086535</v>
       </c>
       <c r="T85">
-        <v>5.733969742272834</v>
+        <v>6.074084081381177</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.361804048302249</v>
+        <v>2.333687333441508</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8660,22 +8660,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1133563623213845</v>
+        <v>0.1133011828755287</v>
       </c>
       <c r="C86">
-        <v>3.7557906151061</v>
+        <v>3.562739238918311</v>
       </c>
       <c r="D86">
-        <v>19.8769906151061</v>
+        <v>19.89323923891831</v>
       </c>
       <c r="E86">
-        <v>10.9512</v>
+        <v>11.1605</v>
       </c>
       <c r="F86">
-        <v>17.5812</v>
+        <v>17.7905</v>
       </c>
       <c r="G86">
         <v>1.46</v>
@@ -8696,28 +8696,28 @@
         <v>3.11</v>
       </c>
       <c r="M86">
-        <v>1.33265496</v>
+        <v>1.3485199</v>
       </c>
       <c r="N86">
-        <v>1.77734504</v>
+        <v>1.7614801</v>
       </c>
       <c r="O86">
-        <v>0.4265628096</v>
+        <v>0.422755224</v>
       </c>
       <c r="P86">
-        <v>1.3507822304</v>
+        <v>1.338724876</v>
       </c>
       <c r="Q86">
-        <v>2.6907822304</v>
+        <v>2.678724876</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4060352645086533</v>
+        <v>0.4288958858368578</v>
       </c>
       <c r="T86">
-        <v>6.074084081381173</v>
+        <v>6.459546999037293</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.333687333441508</v>
+        <v>2.306232188342197</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8742,22 +8742,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1133011828755287</v>
+        <v>0.1132460034296728</v>
       </c>
       <c r="C87">
-        <v>3.562739238918311</v>
+        <v>3.369714449630035</v>
       </c>
       <c r="D87">
-        <v>19.89323923891831</v>
+        <v>19.90951444963003</v>
       </c>
       <c r="E87">
-        <v>11.1605</v>
+        <v>11.3698</v>
       </c>
       <c r="F87">
-        <v>17.7905</v>
+        <v>17.9998</v>
       </c>
       <c r="G87">
         <v>1.46</v>
@@ -8778,28 +8778,28 @@
         <v>3.11</v>
       </c>
       <c r="M87">
-        <v>1.3485199</v>
+        <v>1.36438484</v>
       </c>
       <c r="N87">
-        <v>1.7614801</v>
+        <v>1.74561516</v>
       </c>
       <c r="O87">
-        <v>0.422755224</v>
+        <v>0.4189476383999999</v>
       </c>
       <c r="P87">
-        <v>1.338724876</v>
+        <v>1.3266675216</v>
       </c>
       <c r="Q87">
-        <v>2.678724876</v>
+        <v>2.6666675216</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4288958858368578</v>
+        <v>0.4550223102119486</v>
       </c>
       <c r="T87">
-        <v>6.459546999037293</v>
+        <v>6.900076047787144</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.306232188342197</v>
+        <v>2.27941553498938</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8824,22 +8824,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1132460034296728</v>
+        <v>0.1131908239838169</v>
       </c>
       <c r="C88">
-        <v>3.369714449630035</v>
+        <v>3.176716312549143</v>
       </c>
       <c r="D88">
-        <v>19.90951444963003</v>
+        <v>19.92581631254914</v>
       </c>
       <c r="E88">
-        <v>11.3698</v>
+        <v>11.5791</v>
       </c>
       <c r="F88">
-        <v>17.9998</v>
+        <v>18.2091</v>
       </c>
       <c r="G88">
         <v>1.46</v>
@@ -8860,28 +8860,28 @@
         <v>3.11</v>
       </c>
       <c r="M88">
-        <v>1.36438484</v>
+        <v>1.38024978</v>
       </c>
       <c r="N88">
-        <v>1.74561516</v>
+        <v>1.72975022</v>
       </c>
       <c r="O88">
-        <v>0.4189476383999999</v>
+        <v>0.4151400527999999</v>
       </c>
       <c r="P88">
-        <v>1.3266675216</v>
+        <v>1.3146101672</v>
       </c>
       <c r="Q88">
-        <v>2.6666675216</v>
+        <v>2.6546101672</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4550223102119486</v>
+        <v>0.4851681844908995</v>
       </c>
       <c r="T88">
-        <v>6.900076047787144</v>
+        <v>7.408378796344665</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.27941553498938</v>
+        <v>2.253215356426284</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8906,22 +8906,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1131908239838169</v>
+        <v>0.1131356445379611</v>
       </c>
       <c r="C89">
-        <v>3.176716312549143</v>
+        <v>2.983744893197578</v>
       </c>
       <c r="D89">
-        <v>19.92581631254914</v>
+        <v>19.94214489319758</v>
       </c>
       <c r="E89">
-        <v>11.5791</v>
+        <v>11.7884</v>
       </c>
       <c r="F89">
-        <v>18.2091</v>
+        <v>18.4184</v>
       </c>
       <c r="G89">
         <v>1.46</v>
@@ -8942,28 +8942,28 @@
         <v>3.11</v>
       </c>
       <c r="M89">
-        <v>1.38024978</v>
+        <v>1.39611472</v>
       </c>
       <c r="N89">
-        <v>1.72975022</v>
+        <v>1.71388528</v>
       </c>
       <c r="O89">
-        <v>0.4151400527999999</v>
+        <v>0.4113324672</v>
       </c>
       <c r="P89">
-        <v>1.3146101672</v>
+        <v>1.3025528128</v>
       </c>
       <c r="Q89">
-        <v>2.6546101672</v>
+        <v>2.6425528128</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4851681844908995</v>
+        <v>0.5203383711496756</v>
       </c>
       <c r="T89">
-        <v>7.408378796344665</v>
+        <v>8.001398669661773</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.253215356426284</v>
+        <v>2.227610636466895</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8988,22 +8988,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1131356445379611</v>
+        <v>0.1130804650921052</v>
       </c>
       <c r="C90">
-        <v>2.983744893197578</v>
+        <v>2.79080025731222</v>
       </c>
       <c r="D90">
-        <v>19.94214489319758</v>
+        <v>19.95850025731222</v>
       </c>
       <c r="E90">
-        <v>11.7884</v>
+        <v>11.9977</v>
       </c>
       <c r="F90">
-        <v>18.4184</v>
+        <v>18.6277</v>
       </c>
       <c r="G90">
         <v>1.46</v>
@@ -9024,28 +9024,28 @@
         <v>3.11</v>
       </c>
       <c r="M90">
-        <v>1.39611472</v>
+        <v>1.41197966</v>
       </c>
       <c r="N90">
-        <v>1.71388528</v>
+        <v>1.69802034</v>
       </c>
       <c r="O90">
-        <v>0.4113324672</v>
+        <v>0.4075248815999999</v>
       </c>
       <c r="P90">
-        <v>1.3025528128</v>
+        <v>1.2904954584</v>
       </c>
       <c r="Q90">
-        <v>2.6425528128</v>
+        <v>2.6304954584</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5203383711496756</v>
+        <v>0.5619031372009564</v>
       </c>
       <c r="T90">
-        <v>8.001398669661773</v>
+        <v>8.702240338127446</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.227610636466895</v>
+        <v>2.202581303472884</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9070,22 +9070,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1130804650921052</v>
+        <v>0.1130252856462493</v>
       </c>
       <c r="C91">
-        <v>2.79080025731222</v>
+        <v>2.5978824708458</v>
       </c>
       <c r="D91">
-        <v>19.95850025731222</v>
+        <v>19.9748824708458</v>
       </c>
       <c r="E91">
-        <v>11.9977</v>
+        <v>12.207</v>
       </c>
       <c r="F91">
-        <v>18.6277</v>
+        <v>18.837</v>
       </c>
       <c r="G91">
         <v>1.46</v>
@@ -9106,28 +9106,28 @@
         <v>3.11</v>
       </c>
       <c r="M91">
-        <v>1.41197966</v>
+        <v>1.4278446</v>
       </c>
       <c r="N91">
-        <v>1.69802034</v>
+        <v>1.6821554</v>
       </c>
       <c r="O91">
-        <v>0.4075248815999999</v>
+        <v>0.4037172959999999</v>
       </c>
       <c r="P91">
-        <v>1.2904954584</v>
+        <v>1.278438104</v>
       </c>
       <c r="Q91">
-        <v>2.6304954584</v>
+        <v>2.618438104</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5619031372009564</v>
+        <v>0.6117808564624935</v>
       </c>
       <c r="T91">
-        <v>8.702240338127446</v>
+        <v>9.543250340286255</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.202581303472884</v>
+        <v>2.178108177878741</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9152,22 +9152,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1130252856462493</v>
+        <v>0.1129701062003935</v>
       </c>
       <c r="C92">
-        <v>2.5978824708458</v>
+        <v>2.404991599967754</v>
       </c>
       <c r="D92">
-        <v>19.9748824708458</v>
+        <v>19.99129159996775</v>
       </c>
       <c r="E92">
-        <v>12.207</v>
+        <v>12.4163</v>
       </c>
       <c r="F92">
-        <v>18.837</v>
+        <v>19.0463</v>
       </c>
       <c r="G92">
         <v>1.46</v>
@@ -9188,28 +9188,28 @@
         <v>3.11</v>
       </c>
       <c r="M92">
-        <v>1.4278446</v>
+        <v>1.44370954</v>
       </c>
       <c r="N92">
-        <v>1.6821554</v>
+        <v>1.66629046</v>
       </c>
       <c r="O92">
-        <v>0.4037172959999999</v>
+        <v>0.3999097104</v>
       </c>
       <c r="P92">
-        <v>1.278438104</v>
+        <v>1.2663807496</v>
       </c>
       <c r="Q92">
-        <v>2.618438104</v>
+        <v>2.6063807496</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6117808564624935</v>
+        <v>0.6727425133377054</v>
       </c>
       <c r="T92">
-        <v>9.543250340286255</v>
+        <v>10.57115145403591</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.178108177878741</v>
+        <v>2.154172923176777</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9234,22 +9234,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1129701062003935</v>
+        <v>0.1129149267545376</v>
       </c>
       <c r="C93">
-        <v>2.404991599967754</v>
+        <v>2.212127711065111</v>
       </c>
       <c r="D93">
-        <v>19.99129159996775</v>
+        <v>20.00772771106511</v>
       </c>
       <c r="E93">
-        <v>12.4163</v>
+        <v>12.6256</v>
       </c>
       <c r="F93">
-        <v>19.0463</v>
+        <v>19.2556</v>
       </c>
       <c r="G93">
         <v>1.46</v>
@@ -9270,28 +9270,28 @@
         <v>3.11</v>
       </c>
       <c r="M93">
-        <v>1.44370954</v>
+        <v>1.45957448</v>
       </c>
       <c r="N93">
-        <v>1.66629046</v>
+        <v>1.65042552</v>
       </c>
       <c r="O93">
-        <v>0.3999097104</v>
+        <v>0.3961021247999999</v>
       </c>
       <c r="P93">
-        <v>1.2663807496</v>
+        <v>1.2543233952</v>
       </c>
       <c r="Q93">
-        <v>2.6063807496</v>
+        <v>2.5943233952</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6727425133377054</v>
+        <v>0.7489445844317205</v>
       </c>
       <c r="T93">
-        <v>10.57115145403591</v>
+        <v>11.85602784622298</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.154172923176777</v>
+        <v>2.130758000098768</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1129149267545376</v>
+        <v>0.1128597473086818</v>
       </c>
       <c r="C94">
-        <v>2.212127711065111</v>
+        <v>2.01929087074345</v>
       </c>
       <c r="D94">
-        <v>20.00772771106511</v>
+        <v>20.02419087074345</v>
       </c>
       <c r="E94">
-        <v>12.6256</v>
+        <v>12.8349</v>
       </c>
       <c r="F94">
-        <v>19.2556</v>
+        <v>19.4649</v>
       </c>
       <c r="G94">
         <v>1.46</v>
@@ -9352,28 +9352,28 @@
         <v>3.11</v>
       </c>
       <c r="M94">
-        <v>1.45957448</v>
+        <v>1.47543942</v>
       </c>
       <c r="N94">
-        <v>1.65042552</v>
+        <v>1.63456058</v>
       </c>
       <c r="O94">
-        <v>0.3961021247999999</v>
+        <v>0.3922945392</v>
       </c>
       <c r="P94">
-        <v>1.2543233952</v>
+        <v>1.2422660408</v>
       </c>
       <c r="Q94">
-        <v>2.5943233952</v>
+        <v>2.5822660408</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7489445844317205</v>
+        <v>0.8469186758383112</v>
       </c>
       <c r="T94">
-        <v>11.85602784622298</v>
+        <v>13.50801177903492</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.130758000098768</v>
+        <v>2.10784662375362</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9398,22 +9398,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1128597473086818</v>
+        <v>0.1128045678628259</v>
       </c>
       <c r="C95">
-        <v>2.01929087074345</v>
+        <v>1.826481145827703</v>
       </c>
       <c r="D95">
-        <v>20.02419087074345</v>
+        <v>20.0406811458277</v>
       </c>
       <c r="E95">
-        <v>12.8349</v>
+        <v>13.0442</v>
       </c>
       <c r="F95">
-        <v>19.4649</v>
+        <v>19.6742</v>
       </c>
       <c r="G95">
         <v>1.46</v>
@@ -9434,28 +9434,28 @@
         <v>3.11</v>
       </c>
       <c r="M95">
-        <v>1.47543942</v>
+        <v>1.49130436</v>
       </c>
       <c r="N95">
-        <v>1.63456058</v>
+        <v>1.61869564</v>
       </c>
       <c r="O95">
-        <v>0.3922945392</v>
+        <v>0.3884869535999999</v>
       </c>
       <c r="P95">
-        <v>1.2422660408</v>
+        <v>1.2302086864</v>
       </c>
       <c r="Q95">
-        <v>2.5822660408</v>
+        <v>2.5702086864</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8469186758383112</v>
+        <v>0.9775507977137655</v>
       </c>
       <c r="T95">
-        <v>13.50801177903492</v>
+        <v>15.71065702278418</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.10784662375362</v>
+        <v>2.085422723500922</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9480,22 +9480,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1128045678628259</v>
+        <v>0.11274938841697</v>
       </c>
       <c r="C96">
-        <v>1.826481145827703</v>
+        <v>1.63369860336314</v>
       </c>
       <c r="D96">
-        <v>20.0406811458277</v>
+        <v>20.05719860336314</v>
       </c>
       <c r="E96">
-        <v>13.0442</v>
+        <v>13.2535</v>
       </c>
       <c r="F96">
-        <v>19.6742</v>
+        <v>19.8835</v>
       </c>
       <c r="G96">
         <v>1.46</v>
@@ -9516,28 +9516,28 @@
         <v>3.11</v>
       </c>
       <c r="M96">
-        <v>1.49130436</v>
+        <v>1.5071693</v>
       </c>
       <c r="N96">
-        <v>1.61869564</v>
+        <v>1.6028307</v>
       </c>
       <c r="O96">
-        <v>0.3884869535999999</v>
+        <v>0.3846793679999999</v>
       </c>
       <c r="P96">
-        <v>1.2302086864</v>
+        <v>1.218151332</v>
       </c>
       <c r="Q96">
-        <v>2.5702086864</v>
+        <v>2.558151332</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9775507977137655</v>
+        <v>1.160435768339402</v>
       </c>
       <c r="T96">
-        <v>15.71065702278418</v>
+        <v>18.79436036403316</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.085422723500922</v>
+        <v>2.063470905358807</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9562,22 +9562,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.11274938841697</v>
+        <v>0.1126942089711142</v>
       </c>
       <c r="C97">
-        <v>1.63369860336314</v>
+        <v>1.440943310616241</v>
       </c>
       <c r="D97">
-        <v>20.05719860336314</v>
+        <v>20.07374331061624</v>
       </c>
       <c r="E97">
-        <v>13.2535</v>
+        <v>13.4628</v>
       </c>
       <c r="F97">
-        <v>19.8835</v>
+        <v>20.0928</v>
       </c>
       <c r="G97">
         <v>1.46</v>
@@ -9598,28 +9598,28 @@
         <v>3.11</v>
       </c>
       <c r="M97">
-        <v>1.5071693</v>
+        <v>1.52303424</v>
       </c>
       <c r="N97">
-        <v>1.6028307</v>
+        <v>1.58696576</v>
       </c>
       <c r="O97">
-        <v>0.3846793679999999</v>
+        <v>0.3808717823999999</v>
       </c>
       <c r="P97">
-        <v>1.218151332</v>
+        <v>1.2060939776</v>
       </c>
       <c r="Q97">
-        <v>2.558151332</v>
+        <v>2.5460939776</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.160435768339402</v>
+        <v>1.434763224277856</v>
       </c>
       <c r="T97">
-        <v>18.79436036403316</v>
+        <v>23.41991537590661</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.063470905358807</v>
+        <v>2.04197641676132</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9644,22 +9644,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1126942089711142</v>
+        <v>0.1126390295252583</v>
       </c>
       <c r="C98">
-        <v>1.440943310616241</v>
+        <v>1.248215335075599</v>
       </c>
       <c r="D98">
-        <v>20.07374331061624</v>
+        <v>20.0903153350756</v>
       </c>
       <c r="E98">
-        <v>13.4628</v>
+        <v>13.6721</v>
       </c>
       <c r="F98">
-        <v>20.0928</v>
+        <v>20.3021</v>
       </c>
       <c r="G98">
         <v>1.46</v>
@@ -9680,28 +9680,28 @@
         <v>3.11</v>
       </c>
       <c r="M98">
-        <v>1.52303424</v>
+        <v>1.53889918</v>
       </c>
       <c r="N98">
-        <v>1.58696576</v>
+        <v>1.57110082</v>
       </c>
       <c r="O98">
-        <v>0.3808717823999999</v>
+        <v>0.3770641968</v>
       </c>
       <c r="P98">
-        <v>1.2060939776</v>
+        <v>1.1940366232</v>
       </c>
       <c r="Q98">
-        <v>2.5460939776</v>
+        <v>2.5340366232</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.434763224277853</v>
+        <v>1.891975650841941</v>
       </c>
       <c r="T98">
-        <v>23.41991537590655</v>
+        <v>31.12917372902894</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.04197641676132</v>
+        <v>2.020925113495739</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9726,22 +9726,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1126390295252583</v>
+        <v>0.1125838500794024</v>
       </c>
       <c r="C99">
-        <v>1.248215335075599</v>
+        <v>1.055514744452886</v>
       </c>
       <c r="D99">
-        <v>20.0903153350756</v>
+        <v>20.10691474445288</v>
       </c>
       <c r="E99">
-        <v>13.6721</v>
+        <v>13.8814</v>
       </c>
       <c r="F99">
-        <v>20.3021</v>
+        <v>20.5114</v>
       </c>
       <c r="G99">
         <v>1.46</v>
@@ -9762,28 +9762,28 @@
         <v>3.11</v>
       </c>
       <c r="M99">
-        <v>1.53889918</v>
+        <v>1.55476412</v>
       </c>
       <c r="N99">
-        <v>1.57110082</v>
+        <v>1.55523588</v>
       </c>
       <c r="O99">
-        <v>0.3770641968</v>
+        <v>0.3732566112</v>
       </c>
       <c r="P99">
-        <v>1.1940366232</v>
+        <v>1.1819792688</v>
       </c>
       <c r="Q99">
-        <v>2.5340366232</v>
+        <v>2.5219792688</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.891975650841941</v>
+        <v>2.806400503970119</v>
       </c>
       <c r="T99">
-        <v>31.12917372902894</v>
+        <v>46.54769043527372</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.020925113495739</v>
+        <v>2.00030342866415</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9808,22 +9808,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1125838500794024</v>
+        <v>0.1232127506335466</v>
       </c>
       <c r="C100">
-        <v>1.055514744452886</v>
+        <v>-1.914498387691417</v>
       </c>
       <c r="D100">
-        <v>20.10691474445288</v>
+        <v>17.34620161230858</v>
       </c>
       <c r="E100">
-        <v>13.8814</v>
+        <v>14.0907</v>
       </c>
       <c r="F100">
-        <v>20.5114</v>
+        <v>20.7207</v>
       </c>
       <c r="G100">
         <v>1.46</v>
@@ -9844,129 +9844,47 @@
         <v>3.11</v>
       </c>
       <c r="M100">
-        <v>1.55476412</v>
+        <v>1.864863</v>
       </c>
       <c r="N100">
-        <v>1.55523588</v>
+        <v>1.245137</v>
       </c>
       <c r="O100">
-        <v>0.3732566112</v>
+        <v>0.29883288</v>
       </c>
       <c r="P100">
-        <v>1.1819792688</v>
+        <v>0.94630412</v>
       </c>
       <c r="Q100">
-        <v>2.5219792688</v>
+        <v>2.28630412</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.806400503970119</v>
+        <v>5.549675063354651</v>
       </c>
       <c r="T100">
-        <v>46.54769043527372</v>
+        <v>92.80324055400807</v>
       </c>
       <c r="U100">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V100">
         <v>0.24</v>
       </c>
       <c r="W100">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.00030342866415</v>
+        <v>1.667682827103117</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1232127506335466</v>
-      </c>
-      <c r="C101">
-        <v>-1.914498387691417</v>
-      </c>
-      <c r="D101">
-        <v>17.34620161230858</v>
-      </c>
-      <c r="E101">
-        <v>14.0907</v>
-      </c>
-      <c r="F101">
-        <v>20.7207</v>
-      </c>
-      <c r="G101">
-        <v>1.46</v>
-      </c>
-      <c r="H101">
-        <v>14.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.45</v>
-      </c>
-      <c r="K101">
-        <v>1.34</v>
-      </c>
-      <c r="L101">
-        <v>3.11</v>
-      </c>
-      <c r="M101">
-        <v>1.864863</v>
-      </c>
-      <c r="N101">
-        <v>1.245137</v>
-      </c>
-      <c r="O101">
-        <v>0.29883288</v>
-      </c>
-      <c r="P101">
-        <v>0.94630412</v>
-      </c>
-      <c r="Q101">
-        <v>2.28630412</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.549675063354651</v>
-      </c>
-      <c r="T101">
-        <v>92.80324055400807</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.0684</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.667682827103117</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
